--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -228,6 +228,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Panels lose ~0.5%/yr efficiency. Year 10 output is ~95% of Year 1. Must model declining generation.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0" shapeId="0">
+      <text>
+        <t>Battery capacity degrades faster than solar (~2-3%/yr). Augmentation in Y5-7 restores capacity to meet PPA.</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -597,6 +642,11 @@
           <t>30% Investment Tax Credit reduces equity requirement. Government subsidy makes project economics work.</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investment Tax Credit %</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="20" t="inlineStr"/>
@@ -633,6 +683,11 @@
           <t>Solar panels lose efficiency over time. Y10 generation is ~95% of Y1. Must model declining output.</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Annual output loss %</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
@@ -645,6 +700,11 @@
           <t>Contracted cash flows allow sculpting - size debt service to hit target DSCR. More efficient than sweep.</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
@@ -655,6 +715,11 @@
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t>ITC is a 'source' that offsets equity. Pre-ITC Equity - ITC = Net Equity (your actual check).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investment Tax Credit %</t>
         </is>
       </c>
     </row>
@@ -717,6 +782,11 @@
         </is>
       </c>
       <c r="B21" s="24" t="n"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Battery replacement capex</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
@@ -740,6 +810,10 @@
         <is>
           <t>Y7 CFADS reduced by augmentation capex. Check that DSCR still passes in that year.</t>
         </is>
+      </c>
+      <c r="C23">
+        <f> EBITDA − Taxes</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -813,6 +887,11 @@
           <t>Contracted cash flows are predictable, allowing efficient sculpting. Sweeps are for volatile merchant assets.</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
@@ -826,8 +905,136 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -236,39 +236,14 @@
     <author>Lotus Infrastructure</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0">
+    <comment ref="C11" authorId="0" shapeId="0">
       <text>
-        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
-      <text>
-        <t>Panels lose ~0.5%/yr efficiency. Year 10 output is ~95% of Year 1. Must model declining generation.</t>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
-      <text>
-        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
-      </text>
-    </comment>
-    <comment ref="C21" authorId="0" shapeId="0">
-      <text>
-        <t>Battery capacity degrades faster than solar (~2-3%/yr). Augmentation in Y5-7 restores capacity to meet PPA.</t>
+        <t>Largest variable cost for thermal plants. Divide by 1E9 to convert to $mm.</t>
       </text>
     </comment>
     <comment ref="C23" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
-      </text>
-    </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
   </commentList>
@@ -642,11 +617,6 @@
           <t>30% Investment Tax Credit reduces equity requirement. Government subsidy makes project economics work.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Investment Tax Credit %</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="20" t="inlineStr"/>
@@ -671,6 +641,11 @@
           <t>Sun is free. No commodity exposure. Gross margin = revenue - O&amp;M only.</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gen × HR × Gas / 1E9</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
@@ -683,11 +658,6 @@
           <t>Solar panels lose efficiency over time. Y10 generation is ~95% of Y1. Must model declining output.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual output loss %</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
@@ -700,11 +670,6 @@
           <t>Contracted cash flows allow sculpting - size debt service to hit target DSCR. More efficient than sweep.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>% of excess cash to prepay</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
@@ -715,11 +680,6 @@
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t>ITC is a 'source' that offsets equity. Pre-ITC Equity - ITC = Net Equity (your actual check).</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Investment Tax Credit %</t>
         </is>
       </c>
     </row>
@@ -782,11 +742,6 @@
         </is>
       </c>
       <c r="B21" s="24" t="n"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Battery replacement capex</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
@@ -811,9 +766,10 @@
           <t>Y7 CFADS reduced by augmentation capex. Check that DSCR still passes in that year.</t>
         </is>
       </c>
-      <c r="C23">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -885,11 +841,6 @@
       <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Contracted cash flows are predictable, allowing efficient sculpting. Sweeps are for volatile merchant assets.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>% of excess cash to prepay</t>
         </is>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +54,13 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="7">
@@ -110,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,6 +163,8 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -856,133 +867,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -990,6 +874,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: SolarBESS ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>150 MW solar + 75MW BESS in ERCOT at $280mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IC MEMO - COACHING FRAMEWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>1. EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Tip: Lead with IRR and recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>2. TRANSACTION OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Tip: Sources &amp; uses, debt terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>3. INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Tip: 3-4 bullets on attractiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>4. KEY RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Tip: Market, operational, regulatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>5. MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Tip: Hedging, contracts, structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>6. SENSITIVITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Tip: ±10-20% on key inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>7. RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Tip: Clear yes/no with walk-away price</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1138,7 +1273,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="27">
-        <f>MIN(E82:N82)</f>
+        <f>IF(COUNTIF(E82:N82,"&gt;0")&gt;0,MINIFS(E82:N82,E82:N82,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -2391,6 +2391,7 @@
         <v/>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2448,6 +2449,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -2501,6 +2503,7 @@
         <v/>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
@@ -2538,43 +2541,43 @@
         </is>
       </c>
       <c r="E71" s="16">
-        <f>IF(1&lt;=$D$50,0,E68*$D$51)</f>
+        <f>IF(1&lt;=$D$50,0,MAX(0,E68)*$D$51)</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>IF(2&lt;=$D$50,0,F68*$D$51)</f>
+        <f>IF(2&lt;=$D$50,0,MAX(0,F68)*$D$51)</f>
         <v/>
       </c>
       <c r="G71" s="16">
-        <f>IF(3&lt;=$D$50,0,G68*$D$51)</f>
+        <f>IF(3&lt;=$D$50,0,MAX(0,G68)*$D$51)</f>
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>IF(4&lt;=$D$50,0,H68*$D$51)</f>
+        <f>IF(4&lt;=$D$50,0,MAX(0,H68)*$D$51)</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>IF(5&lt;=$D$50,0,I68*$D$51)</f>
+        <f>IF(5&lt;=$D$50,0,MAX(0,I68)*$D$51)</f>
         <v/>
       </c>
       <c r="J71" s="16">
-        <f>IF(6&lt;=$D$50,0,J68*$D$51)</f>
+        <f>IF(6&lt;=$D$50,0,MAX(0,J68)*$D$51)</f>
         <v/>
       </c>
       <c r="K71" s="16">
-        <f>IF(7&lt;=$D$50,0,K68*$D$51)</f>
+        <f>IF(7&lt;=$D$50,0,MAX(0,K68)*$D$51)</f>
         <v/>
       </c>
       <c r="L71" s="16">
-        <f>IF(8&lt;=$D$50,0,L68*$D$51)</f>
+        <f>IF(8&lt;=$D$50,0,MAX(0,L68)*$D$51)</f>
         <v/>
       </c>
       <c r="M71" s="16">
-        <f>IF(9&lt;=$D$50,0,M68*$D$51)</f>
+        <f>IF(9&lt;=$D$50,0,MAX(0,M68)*$D$51)</f>
         <v/>
       </c>
       <c r="N71" s="16">
-        <f>IF(10&lt;=$D$50,0,N68*$D$51)</f>
+        <f>IF(10&lt;=$D$50,0,MAX(0,N68)*$D$51)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,6 +165,12 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -239,26 +245,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Lotus Infrastructure</author>
-  </authors>
-  <commentList>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>Largest variable cost for thermal plants. Divide by 1E9 to convert to $mm.</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,326 +536,632 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:A107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>SOLAR+BESS MODEL - INTUITION GUIDE</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="20" t="inlineStr"/>
-      <c r="B2" s="21" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>SECTION</t>
-        </is>
-      </c>
-      <c r="B3" s="22" t="inlineStr">
-        <is>
-          <t>WHY IT MATTERS / KEY LOGIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="20" t="inlineStr"/>
-      <c r="B4" s="21" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>═══ BUSINESS CONTEXT ═══</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Why Solar + Battery?</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Solar provides contracted PPA revenue. Battery adds arbitrage (buy low/sell high) and ancillary services (grid stability). Combined improves risk-adjusted returns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Revenue Stability</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>PPA contract provides revenue certainty. This supports sculpted debt (vs sweep) because cash flows are predictable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>ITC Impact</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>30% Investment Tax Credit reduces equity requirement. Government subsidy makes project economics work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="20" t="inlineStr"/>
-      <c r="B9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>═══ KEY DIFFERENCES FROM THERMAL ═══</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>No Fuel Cost</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>Sun is free. No commodity exposure. Gross margin = revenue - O&amp;M only.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Gen × HR × Gas / 1E9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Degradation (0.5%/yr)</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Solar panels lose efficiency over time. Y10 generation is ~95% of Y1. Must model declining output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Sculpted vs Sweep Debt</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Contracted cash flows allow sculpting - size debt service to hit target DSCR. More efficient than sweep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>ITC in Sources &amp; Uses</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>ITC is a 'source' that offsets equity. Pre-ITC Equity - ITC = Net Equity (your actual check).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="20" t="inlineStr"/>
-      <c r="B15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>═══ DEBT SCULPTING LOGIC ═══</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>How It Works</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>Target DS = CFADS / Target DSCR. Then: Sculpted Principal = Target DS - Interest. Debt service sized to maintain constant coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Why 1.35x Target?</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Contracted assets get lower DSCR targets (less volatile). 1.35x provides cushion while maximizing debt capacity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Benefit</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>Efficient structure - pay principal when you have cash, not on fixed schedule. Better matches asset profile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="20" t="inlineStr"/>
-      <c r="B20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>═══ BESS AUGMENTATION ═══</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Why Y7 Capex?</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Battery capacity degrades over time. Augmentation restores capacity to maintain contracted services. Budget $5mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Impact on CFADS</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Y7 CFADS reduced by augmentation capex. Check that DSCR still passes in that year.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="20" t="inlineStr"/>
-      <c r="B24" s="21" t="inlineStr"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>═══ TAX TREATMENT ═══</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>MACRS Shield Y1-Y6</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>Accelerated depreciation creates tax losses, shielding income. Zero cash taxes early years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>Post-MACRS (Y7+)</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>MACRS exhausted. Now pay taxes, but at reduced effective rate (15% vs 25%) due to remaining depreciation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="20" t="inlineStr"/>
-      <c r="B28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>═══ COMMON IC QUESTIONS ═══</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>Q: What happens if panels degrade faster?</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>Lower generation = lower PPA revenue. Run sensitivity on degradation rate showing EBITDA and DSCR impact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>Q: Why sculpted vs sweep?</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>Contracted cash flows are predictable, allowing efficient sculpting. Sweeps are for volatile merchant assets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Q: What's BESS basis risk?</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>Battery revenue depends on price volatility. Low volatility = less arbitrage opportunity. PPA hedges this.</t>
+    <row r="1">
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: SOLAR PV + BATTERY ENERGY STORAGE ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Year 0 (2025): Transaction close Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): First full year; PPA Year 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 13 (2038): PPA expiration; merchant transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Year 15 (2040): End of typical solar asset life</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating a 150 MW solar PV facility
+with co-located 75 MW / 300 MWh battery storage in ERCOT West zone. The
+project achieved COD in Q1 2024 (operating ~2 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>The solar facility has a 15-year fixed-price PPA at $35/MWh with an IG utility
+offtaker (A- rating). Approximately 13 years remain from close. Post-PPA
+revenue depends on merchant market conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>The battery generates revenue through energy arbitrage and ancillary services,
+limited to ~365 cycles/year for warranty preservation. The project received
+30% ITC at COD (already monetized) with MACRS depreciation through Year 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>The seller is asking $280mm with bids due by February 28, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>* PPA Price/Tenor: Contracted revenue at $35/MWh for 13 remaining years</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Degradation: 0.5%/year panel efficiency loss - compounds over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Battery Cycling: 365 cycles/year limit; affects arbitrage opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Post-PPA Merchant: Tail value uncertain; conservative assumptions key</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR SOLAR+BESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>- NO fuel cost - margins effectively 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>- Degradation reduces output each year (compounds!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>- PPA provides contracted revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>- Tax treatment: ITC taken, MACRS shield through Y6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Solar Capacity: 150 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capacity Factor: 25-28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Degradation: 0.5%/year (COMPOUNDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - PPA Price: $35/MWh (fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - PPA Tenor: 13 years remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Post-PPA Price: Conservative merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>2. BUILD GENERATION WITH DEGRADATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Year 1 Generation = Capacity x CF x 8760</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Year n Generation = Year 1 x (1 - Degradation)^(n-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Example: Y10 = Y1 x 0.995^9 = ~95.6% of Y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>3. BUILD TAX SCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Years 1-6: MACRS shield = ZERO taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Years 7+: Normal taxation</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Formula: =IF(Year &lt;= Shield_Years, 0, MAX(0, EBIT) x Rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="34" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>4. SCULPTED DEBT (NOT Cash Sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Solar+BESS with PPA uses SCULPTED debt:</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Cash flows predictable (contracted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Lenders comfortable with 1.30-1.40x DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sculpted Principal = MIN(MAX(0, CFADS/Target_DSCR - Interest), Beg_Bal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SCULPTED DEBT - NO CIRCULARITY ISSUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unlike cash sweep, sculpted debt is calculated FROM CFADS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1. Know CFADS (revenue - opex - taxes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2. Calculate Target DS = CFADS / Target DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3. Calculate Principal = Target DS - Interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4. DSRA Target references this known DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>No circular loop because everything flows from CFADS downward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A. Tax Equity Partnership:</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If ITC not yet monetized</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Complex waterfall with flip date</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B. Merchant Solar (No PPA):</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Much riskier - lower leverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - May not be financeable with project debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C. Standalone BESS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - No solar, just storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Revenue from pure arbitrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1. Degradation compounds correctly (Y10 &lt; 95% of Y1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2. Tax is $0 for MACRS shield years</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3. Tax formula has MAX(0,...) guardrail</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4. PPA revenue switches to merchant at correct year</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5. DSCR is ~1.30-1.40x (sculpted to target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t>* Degradation at 0.5%/yr means Y10 is ~95.6% of Y1 (not 95%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>* ITC already taken - no tax equity modeling needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="inlineStr">
+        <is>
+          <t>* Post-PPA price should be conservative (70-80% of PPA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>* MACRS shield means ~6 years of zero taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Q: How does 0.5% vs 0.7% annual degradation affect exit value?</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Q: What's your post-PPA merchant assumption and why?</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Q: Why use sculpted debt instead of cash sweep?</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Q: What would make you walk away from this deal?</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1155,38 +1447,60 @@
           <t>Solar+BESS Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="33" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="33" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="33" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="33" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="33" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="33" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="33" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="33" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -2391,7 +2705,6 @@
         <v/>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2449,7 +2762,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -2503,7 +2815,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +86,12 @@
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -143,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,6 +212,14 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3161,196 +3175,196 @@
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="n"/>
+      <c r="B6" s="46" t="n"/>
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="44" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="n"/>
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="n"/>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="n"/>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="46" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="48" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="46" t="n"/>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="49" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>AVERAGE(E73:N73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="27">
-        <f>IF(COUNTIF(E82:N82,"&gt;0")&gt;0,MINIFS(E82:N82,E82:N82,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="28">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="27">
-        <f>D119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="28">
-        <f>D123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -3363,9 +3377,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -6246,196 +6260,196 @@
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="n"/>
+      <c r="B6" s="46" t="n"/>
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="44" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="n"/>
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="n"/>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="n"/>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="46" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="48" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="46" t="n"/>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="49" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>AVERAGE(E73:N73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="27">
-        <f>IF(COUNTIF(E82:N82,"&gt;0")&gt;0,MINIFS(E82:N82,E82:N82,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="28">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="27">
-        <f>D119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="28">
-        <f>D123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -6448,9 +6462,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,11 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,6 +225,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3037,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3119,46 +3125,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7">
-        <f>$D$17</f>
-        <v/>
-      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Y1 EBITDA</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3168,317 +3164,310 @@
       </c>
       <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="7">
-        <f>E68</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Y1 EBITDA</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>═══════════ CONTROL PANEL ═══════════</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n"/>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="46" t="n"/>
       <c r="B6" s="46" t="n"/>
       <c r="C6" s="46" t="n"/>
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
+      <c r="A7" s="46" t="n"/>
       <c r="B7" s="46" t="n"/>
       <c r="C7" s="46" t="n"/>
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="B8" s="46" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D8" s="44" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="C8" s="46" t="n"/>
+      <c r="D8" s="46" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Contract End Year</t>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B9" s="46" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>0 = pure merchant; else year PPA ends</t>
         </is>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D10" s="44" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="46" t="n"/>
-      <c r="B10" s="46" t="n"/>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="46" t="n"/>
-    </row>
     <row r="11">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>TIMING</t>
-        </is>
-      </c>
+      <c r="A11" s="46" t="n"/>
       <c r="B11" s="46" t="n"/>
       <c r="C11" s="46" t="n"/>
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>TIMING</t>
         </is>
       </c>
       <c r="B12" s="46" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>5 / 7 / 10</t>
-        </is>
-      </c>
-      <c r="D12" s="44" t="n">
-        <v>7</v>
-      </c>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>Tax Credit End Year</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B13" s="46" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D14" s="44" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="46" t="n"/>
-      <c r="B14" s="46" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
+      <c r="A15" s="46" t="n"/>
       <c r="B15" s="46" t="n"/>
       <c r="C15" s="46" t="n"/>
-      <c r="D15" s="48" t="n"/>
+      <c r="D15" s="46" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>Debt Sweep</t>
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B16" s="46" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D16" s="30" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="48" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Sweep %</t>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B17" s="46" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Sweep %</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Active when Sweep = ON</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="46" t="n"/>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="49" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
+      <c r="A19" s="46" t="n"/>
       <c r="B19" s="46" t="n"/>
       <c r="C19" s="46" t="n"/>
-      <c r="D19" s="50" t="n"/>
+      <c r="D19" s="49" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="50" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B21" s="46" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="10">
-        <f>D108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Debt Payoff Y10</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>IF(N81&lt;1,"PASS","FAIL")</f>
+        <f>D108</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Min DSCR ≥ 1.30x</t>
+          <t>Debt Payoff Y10</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.30,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+        <f>IF(N81&lt;1,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Min DSCR ≥ 1.30x</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>TRANSACTION INPUTS</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>145</v>
-      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>0.015</v>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>ITC Rate</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -3488,377 +3477,381 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Investment Tax Credit</t>
+          <t>Legal, advisory, financing</t>
         </is>
       </c>
       <c r="D29" s="29" t="n">
-        <v>0.3</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>ITC Rate</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>On exit year EBITDA</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="n">
-        <v>8</v>
+          <t>Investment Tax Credit</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>On exit year EBITDA</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Exit Year</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Hold period</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D32" s="14" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ASSET INPUTS</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>AC Capacity</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>MWac</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Inverter rating</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>115</v>
-      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Capacity Factor</t>
+          <t>AC Capacity</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MWac</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>P50 estimate</t>
-        </is>
-      </c>
-      <c r="D35" s="29" t="n">
-        <v>0.26</v>
+          <t>Inverter rating</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>Capacity Factor</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>P50 estimate</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Degradation</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Annual output decline</t>
         </is>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D37" s="29" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>PRICING INPUTS</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>PPA Price Y1</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Contracted price</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PPA Escalation</t>
+          <t>PPA Price Y1</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Contract escalation</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>0.015</v>
+          <t>Contracted price</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>BESS Revenue Y1</t>
+          <t>PPA Escalation</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Arbitrage + ancillary</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>4.5</v>
+          <t>Contract escalation</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
+          <t>BESS Revenue Y1</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Arbitrage + ancillary</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>BESS Revenue Escalation</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D43" s="29" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>COST INPUTS</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Cost</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>$mm/yr</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Fixed operating costs</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Escalation</t>
+          <t>O&amp;M Cost</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>$mm/yr</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Cost escalation</t>
-        </is>
-      </c>
-      <c r="D46" s="29" t="n">
-        <v>0.02</v>
+          <t>Fixed operating costs</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Augmentation Year</t>
+          <t>O&amp;M Escalation</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>BESS capacity augment</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>7</v>
+          <t>Cost escalation</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
+          <t>Augmentation Year</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>BESS capacity augment</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
           <t>Augmentation Cost</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Battery replacement</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D49" s="11" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>FINANCING INPUTS</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Leverage</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Entry EV</t>
-        </is>
-      </c>
-      <c r="D51" s="29" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Leverage</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3868,451 +3861,418 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Lower (contracted)</t>
+          <t>Debt / Entry EV</t>
         </is>
       </c>
       <c r="D52" s="29" t="n">
-        <v>0.055</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Longer for contracted</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>10</v>
+          <t>Lower (contracted)</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
+          <t>Longer for contracted</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Target DSCR</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>For sculpting</t>
-        </is>
-      </c>
-      <c r="D55" s="30" t="n">
-        <v>1.35</v>
+          <t>Debt service reserve</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>Target DSCR</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>For sculpting</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
           <t>Lock-up DSCR</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D56" s="30" t="n">
+      <c r="D57" s="30" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>TAX INPUTS</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-      <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Blended federal + state</t>
-        </is>
-      </c>
-      <c r="D59" s="29" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>MACRS Shield Years</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Years with no tax</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>6</v>
+          <t>Blended federal + state</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
+          <t>MACRS Shield Years</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Years with no tax</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
           <t>Post-MACRS Tax Rate</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Reduced effective rate</t>
         </is>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D62" s="29" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>CALCULATED ITEMS</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Y1 Generation</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>MWh</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>AC Cap × CF × 8760</t>
-        </is>
-      </c>
-      <c r="D64" s="15">
-        <f>$D$24*$D$25*8760</f>
-        <v/>
-      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>Y1 Generation</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>MWh</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
-        </is>
-      </c>
-      <c r="D65" s="16">
-        <f>$D$17*$D$41</f>
+          <t>AC Cap × CF × 8760</t>
+        </is>
+      </c>
+      <c r="D65" s="15">
+        <f>$D$24*$D$25*8760</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
+          <t>Debt Amount</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Entry EV × Leverage</t>
+        </is>
+      </c>
+      <c r="D66" s="16">
+        <f>$D$17*$D$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
           <t>ITC Benefit</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>Entry EV × ITC Rate</t>
         </is>
       </c>
-      <c r="D66" s="16">
+      <c r="D67" s="16">
         <f>$D$17*$D$19</f>
         <v/>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>OPERATING MODEL</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Generation</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>MWh</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>With degradation</t>
-        </is>
-      </c>
-      <c r="E69" s="15">
-        <f>$D$54*(1-$D$26)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F69" s="15">
-        <f>$D$54*(1-$D$26)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G69" s="15">
-        <f>$D$54*(1-$D$26)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H69" s="15">
-        <f>$D$54*(1-$D$26)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I69" s="15">
-        <f>$D$54*(1-$D$26)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J69" s="15">
-        <f>$D$54*(1-$D$26)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K69" s="15">
-        <f>$D$54*(1-$D$26)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L69" s="15">
-        <f>$D$54*(1-$D$26)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M69" s="15">
-        <f>$D$54*(1-$D$26)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N69" s="15">
-        <f>$D$54*(1-$D$26)^(10-1)</f>
-        <v/>
-      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>With degradation</t>
+        </is>
+      </c>
+      <c r="E70" s="15">
+        <f>$D$54*(1-$D$26)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F70" s="15">
+        <f>$D$54*(1-$D$26)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G70" s="15">
+        <f>$D$54*(1-$D$26)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H70" s="15">
+        <f>$D$54*(1-$D$26)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I70" s="15">
+        <f>$D$54*(1-$D$26)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J70" s="15">
+        <f>$D$54*(1-$D$26)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K70" s="15">
+        <f>$D$54*(1-$D$26)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L70" s="15">
+        <f>$D$54*(1-$D$26)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M70" s="15">
+        <f>$D$54*(1-$D$26)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N70" s="15">
+        <f>$D$54*(1-$D$26)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>PPA Price</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>$/MWh</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E70" s="16">
+      <c r="E71" s="16">
         <f>$D$29*(1+$D$30)^(1-1)</f>
         <v/>
       </c>
-      <c r="F70" s="16">
+      <c r="F71" s="16">
         <f>$D$29*(1+$D$30)^(2-1)</f>
         <v/>
       </c>
-      <c r="G70" s="16">
+      <c r="G71" s="16">
         <f>$D$29*(1+$D$30)^(3-1)</f>
         <v/>
       </c>
-      <c r="H70" s="16">
+      <c r="H71" s="16">
         <f>$D$29*(1+$D$30)^(4-1)</f>
         <v/>
       </c>
-      <c r="I70" s="16">
+      <c r="I71" s="16">
         <f>$D$29*(1+$D$30)^(5-1)</f>
         <v/>
       </c>
-      <c r="J70" s="16">
+      <c r="J71" s="16">
         <f>$D$29*(1+$D$30)^(6-1)</f>
         <v/>
       </c>
-      <c r="K70" s="16">
+      <c r="K71" s="16">
         <f>$D$29*(1+$D$30)^(7-1)</f>
         <v/>
       </c>
-      <c r="L70" s="16">
+      <c r="L71" s="16">
         <f>$D$29*(1+$D$30)^(8-1)</f>
         <v/>
       </c>
-      <c r="M70" s="16">
+      <c r="M71" s="16">
         <f>$D$29*(1+$D$30)^(9-1)</f>
         <v/>
       </c>
-      <c r="N70" s="16">
+      <c r="N71" s="16">
         <f>$D$29*(1+$D$30)^(10-1)</f>
         <v/>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>PPA Revenue</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Gen × PPA Price / 1M</t>
-        </is>
-      </c>
-      <c r="E72" s="16">
-        <f>E59*E60/1000000</f>
-        <v/>
-      </c>
-      <c r="F72" s="16">
-        <f>F59*F60/1000000</f>
-        <v/>
-      </c>
-      <c r="G72" s="16">
-        <f>G59*G60/1000000</f>
-        <v/>
-      </c>
-      <c r="H72" s="16">
-        <f>H59*H60/1000000</f>
-        <v/>
-      </c>
-      <c r="I72" s="16">
-        <f>I59*I60/1000000</f>
-        <v/>
-      </c>
-      <c r="J72" s="16">
-        <f>J59*J60/1000000</f>
-        <v/>
-      </c>
-      <c r="K72" s="16">
-        <f>K59*K60/1000000</f>
-        <v/>
-      </c>
-      <c r="L72" s="16">
-        <f>L59*L60/1000000</f>
-        <v/>
-      </c>
-      <c r="M72" s="16">
-        <f>M59*M60/1000000</f>
-        <v/>
-      </c>
-      <c r="N72" s="16">
-        <f>N59*N60/1000000</f>
-        <v/>
-      </c>
-    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>BESS Revenue</t>
+          <t>PPA Revenue</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -4322,294 +4282,177 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Arbitrage + ancillary</t>
-        </is>
-      </c>
-      <c r="E73" s="16">
-        <f>$D$31*(1+$D$32)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F73" s="16">
-        <f>$D$31*(1+$D$32)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G73" s="16">
-        <f>$D$31*(1+$D$32)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H73" s="16">
-        <f>$D$31*(1+$D$32)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I73" s="16">
-        <f>$D$31*(1+$D$32)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J73" s="16">
-        <f>$D$31*(1+$D$32)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K73" s="16">
-        <f>$D$31*(1+$D$32)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L73" s="16">
-        <f>$D$31*(1+$D$32)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M73" s="16">
-        <f>$D$31*(1+$D$32)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N73" s="16">
-        <f>$D$31*(1+$D$32)^(10-1)</f>
-        <v/>
-      </c>
+          <t>Gen × PPA Price / 1M</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr"/>
+      <c r="F73" s="16" t="inlineStr"/>
+      <c r="G73" s="16" t="inlineStr"/>
+      <c r="H73" s="16" t="inlineStr"/>
+      <c r="I73" s="16" t="inlineStr"/>
+      <c r="J73" s="16" t="inlineStr"/>
+      <c r="K73" s="16" t="inlineStr"/>
+      <c r="L73" s="16" t="inlineStr"/>
+      <c r="M73" s="16" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
+          <t>BESS Revenue</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Arbitrage + ancillary</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr"/>
+      <c r="F74" s="16" t="inlineStr"/>
+      <c r="G74" s="16" t="inlineStr"/>
+      <c r="H74" s="16" t="inlineStr"/>
+      <c r="I74" s="16" t="inlineStr"/>
+      <c r="J74" s="16" t="inlineStr"/>
+      <c r="K74" s="16" t="inlineStr"/>
+      <c r="L74" s="16" t="inlineStr"/>
+      <c r="M74" s="16" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr"/>
-      <c r="E74" s="17">
-        <f>E62+E63</f>
-        <v/>
-      </c>
-      <c r="F74" s="17">
-        <f>F62+F63</f>
-        <v/>
-      </c>
-      <c r="G74" s="17">
-        <f>G62+G63</f>
-        <v/>
-      </c>
-      <c r="H74" s="17">
-        <f>H62+H63</f>
-        <v/>
-      </c>
-      <c r="I74" s="17">
-        <f>I62+I63</f>
-        <v/>
-      </c>
-      <c r="J74" s="17">
-        <f>J62+J63</f>
-        <v/>
-      </c>
-      <c r="K74" s="17">
-        <f>K62+K63</f>
-        <v/>
-      </c>
-      <c r="L74" s="17">
-        <f>L62+L63</f>
-        <v/>
-      </c>
-      <c r="M74" s="17">
-        <f>M62+M63</f>
-        <v/>
-      </c>
-      <c r="N74" s="17">
-        <f>N62+N63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr"/>
+      <c r="E75" s="17" t="inlineStr"/>
+      <c r="F75" s="17" t="inlineStr"/>
+      <c r="G75" s="17" t="inlineStr"/>
+      <c r="H75" s="17" t="inlineStr"/>
+      <c r="I75" s="17" t="inlineStr"/>
+      <c r="J75" s="17" t="inlineStr"/>
+      <c r="K75" s="17" t="inlineStr"/>
+      <c r="L75" s="17" t="inlineStr"/>
+      <c r="M75" s="17" t="inlineStr"/>
+      <c r="N75" s="17" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>O&amp;M Cost</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E76" s="16">
+      <c r="E77" s="16">
         <f>$D$35*(1+$D$36)^(1-1)</f>
         <v/>
       </c>
-      <c r="F76" s="16">
+      <c r="F77" s="16">
         <f>$D$35*(1+$D$36)^(2-1)</f>
         <v/>
       </c>
-      <c r="G76" s="16">
+      <c r="G77" s="16">
         <f>$D$35*(1+$D$36)^(3-1)</f>
         <v/>
       </c>
-      <c r="H76" s="16">
+      <c r="H77" s="16">
         <f>$D$35*(1+$D$36)^(4-1)</f>
         <v/>
       </c>
-      <c r="I76" s="16">
+      <c r="I77" s="16">
         <f>$D$35*(1+$D$36)^(5-1)</f>
         <v/>
       </c>
-      <c r="J76" s="16">
+      <c r="J77" s="16">
         <f>$D$35*(1+$D$36)^(6-1)</f>
         <v/>
       </c>
-      <c r="K76" s="16">
+      <c r="K77" s="16">
         <f>$D$35*(1+$D$36)^(7-1)</f>
         <v/>
       </c>
-      <c r="L76" s="16">
+      <c r="L77" s="16">
         <f>$D$35*(1+$D$36)^(8-1)</f>
         <v/>
       </c>
-      <c r="M76" s="16">
+      <c r="M77" s="16">
         <f>$D$35*(1+$D$36)^(9-1)</f>
         <v/>
       </c>
-      <c r="N76" s="16">
+      <c r="N77" s="16">
         <f>$D$35*(1+$D$36)^(10-1)</f>
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr"/>
-      <c r="E78" s="7">
-        <f>E64-E66</f>
-        <v/>
-      </c>
-      <c r="F78" s="7">
-        <f>F64-F66</f>
-        <v/>
-      </c>
-      <c r="G78" s="7">
-        <f>G64-G66</f>
-        <v/>
-      </c>
-      <c r="H78" s="7">
-        <f>H64-H66</f>
-        <v/>
-      </c>
-      <c r="I78" s="7">
-        <f>I64-I66</f>
-        <v/>
-      </c>
-      <c r="J78" s="7">
-        <f>J64-J66</f>
-        <v/>
-      </c>
-      <c r="K78" s="7">
-        <f>K64-K66</f>
-        <v/>
-      </c>
-      <c r="L78" s="7">
-        <f>L64-L66</f>
-        <v/>
-      </c>
-      <c r="M78" s="7">
-        <f>M64-M66</f>
-        <v/>
-      </c>
-      <c r="N78" s="7">
-        <f>N64-N66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr"/>
+      <c r="E79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
+      <c r="L79" s="7" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+      <c r="N79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>MACRS shield Y1-Y6</t>
-        </is>
-      </c>
-      <c r="E81" s="16">
-        <f>IF(1&lt;=$D$50,0,MAX(0,E68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="F81" s="16">
-        <f>IF(2&lt;=$D$50,0,MAX(0,F68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="G81" s="16">
-        <f>IF(3&lt;=$D$50,0,MAX(0,G68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="H81" s="16">
-        <f>IF(4&lt;=$D$50,0,MAX(0,H68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="I81" s="16">
-        <f>IF(5&lt;=$D$50,0,MAX(0,I68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="J81" s="16">
-        <f>IF(6&lt;=$D$50,0,MAX(0,J68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="K81" s="16">
-        <f>IF(7&lt;=$D$50,0,MAX(0,K68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="L81" s="16">
-        <f>IF(8&lt;=$D$50,0,MAX(0,L68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="M81" s="16">
-        <f>IF(9&lt;=$D$50,0,MAX(0,M68)*$D$51)</f>
-        <v/>
-      </c>
-      <c r="N81" s="16">
-        <f>IF(10&lt;=$D$50,0,MAX(0,N68)*$D$51)</f>
-        <v/>
-      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>BESS Augmentation</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -4619,184 +4462,129 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Battery replacement</t>
-        </is>
-      </c>
-      <c r="E82" s="18">
-        <f>IF(1=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="F82" s="18">
-        <f>IF(2=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="G82" s="18">
-        <f>IF(3=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="H82" s="18">
-        <f>IF(4=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="I82" s="18">
-        <f>IF(5=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="J82" s="18">
-        <f>IF(6=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="K82" s="18">
-        <f>IF(7=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="L82" s="18">
-        <f>IF(8=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="M82" s="18">
-        <f>IF(9=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="N82" s="18">
-        <f>IF(10=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
+          <t>MACRS shield Y1-Y6</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr"/>
+      <c r="F82" s="16" t="inlineStr"/>
+      <c r="G82" s="16" t="inlineStr"/>
+      <c r="H82" s="16" t="inlineStr"/>
+      <c r="I82" s="16" t="inlineStr"/>
+      <c r="J82" s="16" t="inlineStr"/>
+      <c r="K82" s="16" t="inlineStr"/>
+      <c r="L82" s="16" t="inlineStr"/>
+      <c r="M82" s="16" t="inlineStr"/>
+      <c r="N82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
+          <t>BESS Augmentation</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Battery replacement</t>
+        </is>
+      </c>
+      <c r="E83" s="18">
+        <f>IF(1=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="F83" s="18">
+        <f>IF(2=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="G83" s="18">
+        <f>IF(3=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="H83" s="18">
+        <f>IF(4=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="I83" s="18">
+        <f>IF(5=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="18">
+        <f>IF(6=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="K83" s="18">
+        <f>IF(7=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="L83" s="18">
+        <f>IF(8=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="M83" s="18">
+        <f>IF(9=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+      <c r="N83" s="18">
+        <f>IF(10=$D$37,$D$38,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>EBITDA - Taxes - Augment</t>
         </is>
       </c>
-      <c r="E83" s="7">
-        <f>E68-E71-E72</f>
-        <v/>
-      </c>
-      <c r="F83" s="7">
-        <f>F68-F71-F72</f>
-        <v/>
-      </c>
-      <c r="G83" s="7">
-        <f>G68-G71-G72</f>
-        <v/>
-      </c>
-      <c r="H83" s="7">
-        <f>H68-H71-H72</f>
-        <v/>
-      </c>
-      <c r="I83" s="7">
-        <f>I68-I71-I72</f>
-        <v/>
-      </c>
-      <c r="J83" s="7">
-        <f>J68-J71-J72</f>
-        <v/>
-      </c>
-      <c r="K83" s="7">
-        <f>K68-K71-K72</f>
-        <v/>
-      </c>
-      <c r="L83" s="7">
-        <f>L68-L71-L72</f>
-        <v/>
-      </c>
-      <c r="M83" s="7">
-        <f>M68-M71-M72</f>
-        <v/>
-      </c>
-      <c r="N83" s="7">
-        <f>N68-N71-N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr"/>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
+      <c r="L84" s="7" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+      <c r="N84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>DEBT SCHEDULE (Sculpted to 1.35x DSCR)</t>
         </is>
       </c>
-      <c r="B85" s="4" t="n"/>
-      <c r="C85" s="4" t="n"/>
-      <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="4" t="n"/>
-      <c r="G85" s="4" t="n"/>
-      <c r="H85" s="4" t="n"/>
-      <c r="I85" s="4" t="n"/>
-      <c r="J85" s="4" t="n"/>
-      <c r="K85" s="4" t="n"/>
-      <c r="L85" s="4" t="n"/>
-      <c r="M85" s="4" t="n"/>
-      <c r="N85" s="4" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr"/>
-      <c r="E86" s="16">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="F86" s="16">
-        <f>E81</f>
-        <v/>
-      </c>
-      <c r="G86" s="16">
-        <f>F81</f>
-        <v/>
-      </c>
-      <c r="H86" s="16">
-        <f>G81</f>
-        <v/>
-      </c>
-      <c r="I86" s="16">
-        <f>H81</f>
-        <v/>
-      </c>
-      <c r="J86" s="16">
-        <f>I81</f>
-        <v/>
-      </c>
-      <c r="K86" s="16">
-        <f>J81</f>
-        <v/>
-      </c>
-      <c r="L86" s="16">
-        <f>K81</f>
-        <v/>
-      </c>
-      <c r="M86" s="16">
-        <f>L81</f>
-        <v/>
-      </c>
-      <c r="N86" s="16">
-        <f>M81</f>
-        <v/>
-      </c>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="n"/>
+      <c r="J86" s="4" t="n"/>
+      <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Beginning Balance</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -4804,56 +4592,52 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
+      <c r="C87" s="6" t="inlineStr"/>
       <c r="E87" s="16">
-        <f>E76*$D$42</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="F87" s="16">
-        <f>F76*$D$42</f>
+        <f>E81</f>
         <v/>
       </c>
       <c r="G87" s="16">
-        <f>G76*$D$42</f>
+        <f>F81</f>
         <v/>
       </c>
       <c r="H87" s="16">
-        <f>H76*$D$42</f>
+        <f>G81</f>
         <v/>
       </c>
       <c r="I87" s="16">
-        <f>I76*$D$42</f>
+        <f>H81</f>
         <v/>
       </c>
       <c r="J87" s="16">
-        <f>J76*$D$42</f>
+        <f>I81</f>
         <v/>
       </c>
       <c r="K87" s="16">
-        <f>K76*$D$42</f>
+        <f>J81</f>
         <v/>
       </c>
       <c r="L87" s="16">
-        <f>L76*$D$42</f>
+        <f>K81</f>
         <v/>
       </c>
       <c r="M87" s="16">
-        <f>M76*$D$42</f>
+        <f>L81</f>
         <v/>
       </c>
       <c r="N87" s="16">
-        <f>N76*$D$42</f>
+        <f>M81</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Target Debt Service</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -4863,54 +4647,24 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Target DSCR</t>
-        </is>
-      </c>
-      <c r="E88" s="16">
-        <f>E73/$D$45</f>
-        <v/>
-      </c>
-      <c r="F88" s="16">
-        <f>F73/$D$45</f>
-        <v/>
-      </c>
-      <c r="G88" s="16">
-        <f>G73/$D$45</f>
-        <v/>
-      </c>
-      <c r="H88" s="16">
-        <f>H73/$D$45</f>
-        <v/>
-      </c>
-      <c r="I88" s="16">
-        <f>I73/$D$45</f>
-        <v/>
-      </c>
-      <c r="J88" s="16">
-        <f>J73/$D$45</f>
-        <v/>
-      </c>
-      <c r="K88" s="16">
-        <f>K73/$D$45</f>
-        <v/>
-      </c>
-      <c r="L88" s="16">
-        <f>L73/$D$45</f>
-        <v/>
-      </c>
-      <c r="M88" s="16">
-        <f>M73/$D$45</f>
-        <v/>
-      </c>
-      <c r="N88" s="16">
-        <f>N73/$D$45</f>
-        <v/>
-      </c>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr"/>
+      <c r="F88" s="16" t="inlineStr"/>
+      <c r="G88" s="16" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="16" t="inlineStr"/>
+      <c r="J88" s="16" t="inlineStr"/>
+      <c r="K88" s="16" t="inlineStr"/>
+      <c r="L88" s="16" t="inlineStr"/>
+      <c r="M88" s="16" t="inlineStr"/>
+      <c r="N88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Sculpted Principal</t>
+          <t>Target Debt Service</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4920,54 +4674,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Target DS - Interest</t>
-        </is>
-      </c>
-      <c r="E89" s="16">
-        <f>MIN(MAX(0,E78-E77),E76)</f>
-        <v/>
-      </c>
-      <c r="F89" s="16">
-        <f>MIN(MAX(0,F78-F77),F76)</f>
-        <v/>
-      </c>
-      <c r="G89" s="16">
-        <f>MIN(MAX(0,G78-G77),G76)</f>
-        <v/>
-      </c>
-      <c r="H89" s="16">
-        <f>MIN(MAX(0,H78-H77),H76)</f>
-        <v/>
-      </c>
-      <c r="I89" s="16">
-        <f>MIN(MAX(0,I78-I77),I76)</f>
-        <v/>
-      </c>
-      <c r="J89" s="16">
-        <f>MIN(MAX(0,J78-J77),J76)</f>
-        <v/>
-      </c>
-      <c r="K89" s="16">
-        <f>MIN(MAX(0,K78-K77),K76)</f>
-        <v/>
-      </c>
-      <c r="L89" s="16">
-        <f>MIN(MAX(0,L78-L77),L76)</f>
-        <v/>
-      </c>
-      <c r="M89" s="16">
-        <f>MIN(MAX(0,M78-M77),M76)</f>
-        <v/>
-      </c>
-      <c r="N89" s="16">
-        <f>MIN(MAX(0,N78-N77),N76)</f>
-        <v/>
-      </c>
+          <t>CFADS / Target DSCR</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr"/>
+      <c r="F89" s="16" t="inlineStr"/>
+      <c r="G89" s="16" t="inlineStr"/>
+      <c r="H89" s="16" t="inlineStr"/>
+      <c r="I89" s="16" t="inlineStr"/>
+      <c r="J89" s="16" t="inlineStr"/>
+      <c r="K89" s="16" t="inlineStr"/>
+      <c r="L89" s="16" t="inlineStr"/>
+      <c r="M89" s="16" t="inlineStr"/>
+      <c r="N89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Actual Debt Service</t>
+          <t>Sculpted Principal</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -4977,54 +4701,24 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Interest + Principal</t>
-        </is>
-      </c>
-      <c r="E90" s="16">
-        <f>E77+E79</f>
-        <v/>
-      </c>
-      <c r="F90" s="16">
-        <f>F77+F79</f>
-        <v/>
-      </c>
-      <c r="G90" s="16">
-        <f>G77+G79</f>
-        <v/>
-      </c>
-      <c r="H90" s="16">
-        <f>H77+H79</f>
-        <v/>
-      </c>
-      <c r="I90" s="16">
-        <f>I77+I79</f>
-        <v/>
-      </c>
-      <c r="J90" s="16">
-        <f>J77+J79</f>
-        <v/>
-      </c>
-      <c r="K90" s="16">
-        <f>K77+K79</f>
-        <v/>
-      </c>
-      <c r="L90" s="16">
-        <f>L77+L79</f>
-        <v/>
-      </c>
-      <c r="M90" s="16">
-        <f>M77+M79</f>
-        <v/>
-      </c>
-      <c r="N90" s="16">
-        <f>N77+N79</f>
-        <v/>
-      </c>
+          <t>Target DS - Interest</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr"/>
+      <c r="F90" s="16" t="inlineStr"/>
+      <c r="G90" s="16" t="inlineStr"/>
+      <c r="H90" s="16" t="inlineStr"/>
+      <c r="I90" s="16" t="inlineStr"/>
+      <c r="J90" s="16" t="inlineStr"/>
+      <c r="K90" s="16" t="inlineStr"/>
+      <c r="L90" s="16" t="inlineStr"/>
+      <c r="M90" s="16" t="inlineStr"/>
+      <c r="N90" s="16" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Actual Debt Service</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -5034,192 +4728,129 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Beg - Principal</t>
+          <t>Interest + Principal</t>
         </is>
       </c>
       <c r="E91" s="16">
-        <f>MAX(0,E76-E79)</f>
+        <f>E77+E79</f>
         <v/>
       </c>
       <c r="F91" s="16">
-        <f>MAX(0,F76-F79)</f>
+        <f>F77+F79</f>
         <v/>
       </c>
       <c r="G91" s="16">
-        <f>MAX(0,G76-G79)</f>
+        <f>G77+G79</f>
         <v/>
       </c>
       <c r="H91" s="16">
-        <f>MAX(0,H76-H79)</f>
+        <f>H77+H79</f>
         <v/>
       </c>
       <c r="I91" s="16">
-        <f>MAX(0,I76-I79)</f>
+        <f>I77+I79</f>
         <v/>
       </c>
       <c r="J91" s="16">
-        <f>MAX(0,J76-J79)</f>
+        <f>J77+J79</f>
         <v/>
       </c>
       <c r="K91" s="16">
-        <f>MAX(0,K76-K79)</f>
+        <f>K77+K79</f>
         <v/>
       </c>
       <c r="L91" s="16">
-        <f>MAX(0,L76-L79)</f>
+        <f>L77+L79</f>
         <v/>
       </c>
       <c r="M91" s="16">
-        <f>MAX(0,M76-M79)</f>
+        <f>M77+M79</f>
         <v/>
       </c>
       <c r="N91" s="16">
-        <f>MAX(0,N76-N79)</f>
+        <f>N77+N79</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Beg - Principal</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr"/>
+      <c r="F92" s="16" t="inlineStr"/>
+      <c r="G92" s="16" t="inlineStr"/>
+      <c r="H92" s="16" t="inlineStr"/>
+      <c r="I92" s="16" t="inlineStr"/>
+      <c r="J92" s="16" t="inlineStr"/>
+      <c r="K92" s="16" t="inlineStr"/>
+      <c r="L92" s="16" t="inlineStr"/>
+      <c r="M92" s="16" t="inlineStr"/>
+      <c r="N92" s="16" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
           <t>Actual DSCR</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>CFADS / Actual DS</t>
         </is>
       </c>
-      <c r="E92" s="27">
-        <f>IF(E80&gt;0,E73/E80,0)</f>
-        <v/>
-      </c>
-      <c r="F92" s="27">
-        <f>IF(F80&gt;0,F73/F80,0)</f>
-        <v/>
-      </c>
-      <c r="G92" s="27">
-        <f>IF(G80&gt;0,G73/G80,0)</f>
-        <v/>
-      </c>
-      <c r="H92" s="27">
-        <f>IF(H80&gt;0,H73/H80,0)</f>
-        <v/>
-      </c>
-      <c r="I92" s="27">
-        <f>IF(I80&gt;0,I73/I80,0)</f>
-        <v/>
-      </c>
-      <c r="J92" s="27">
-        <f>IF(J80&gt;0,J73/J80,0)</f>
-        <v/>
-      </c>
-      <c r="K92" s="27">
-        <f>IF(K80&gt;0,K73/K80,0)</f>
-        <v/>
-      </c>
-      <c r="L92" s="27">
-        <f>IF(L80&gt;0,L73/L80,0)</f>
-        <v/>
-      </c>
-      <c r="M92" s="27">
-        <f>IF(M80&gt;0,M73/M80,0)</f>
-        <v/>
-      </c>
-      <c r="N92" s="27">
-        <f>IF(N80&gt;0,N73/N80,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="E93" s="27" t="inlineStr"/>
+      <c r="F93" s="27" t="inlineStr"/>
+      <c r="G93" s="27" t="inlineStr"/>
+      <c r="H93" s="27" t="inlineStr"/>
+      <c r="I93" s="27" t="inlineStr"/>
+      <c r="J93" s="27" t="inlineStr"/>
+      <c r="K93" s="27" t="inlineStr"/>
+      <c r="L93" s="27" t="inlineStr"/>
+      <c r="M93" s="27" t="inlineStr"/>
+      <c r="N93" s="27" t="inlineStr"/>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n"/>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="n"/>
-      <c r="F94" s="4" t="n"/>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="n"/>
-      <c r="I94" s="4" t="n"/>
-      <c r="J94" s="4" t="n"/>
-      <c r="K94" s="4" t="n"/>
-      <c r="L94" s="4" t="n"/>
-      <c r="M94" s="4" t="n"/>
-      <c r="N94" s="4" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D95" s="16">
-        <f>E80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="E95" s="16">
-        <f>F80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="F95" s="16">
-        <f>G80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="G95" s="16">
-        <f>H80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="H95" s="16">
-        <f>I80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="I95" s="16">
-        <f>J80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="J95" s="16">
-        <f>K80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="K95" s="16">
-        <f>L80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="L95" s="16">
-        <f>M80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="M95" s="16">
-        <f>N80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="N95" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -5227,56 +4858,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D96" s="16">
+        <f>E80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="E96" s="16">
+        <f>F80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="F96" s="16">
+        <f>G80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="G96" s="16">
+        <f>H80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="H96" s="16">
+        <f>I80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="I96" s="16">
+        <f>J80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="J96" s="16">
+        <f>K80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="K96" s="16">
+        <f>L80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="L96" s="16">
+        <f>M80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="M96" s="16">
+        <f>N80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="N96" s="16">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E96" s="16">
-        <f>D88</f>
-        <v/>
-      </c>
-      <c r="F96" s="16">
-        <f>E88</f>
-        <v/>
-      </c>
-      <c r="G96" s="16">
-        <f>F88</f>
-        <v/>
-      </c>
-      <c r="H96" s="16">
-        <f>G88</f>
-        <v/>
-      </c>
-      <c r="I96" s="16">
-        <f>H88</f>
-        <v/>
-      </c>
-      <c r="J96" s="16">
-        <f>I88</f>
-        <v/>
-      </c>
-      <c r="K96" s="16">
-        <f>J88</f>
-        <v/>
-      </c>
-      <c r="L96" s="16">
-        <f>K88</f>
-        <v/>
-      </c>
-      <c r="M96" s="16">
-        <f>L88</f>
-        <v/>
-      </c>
-      <c r="N96" s="16">
-        <f>M88</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -5284,354 +4919,366 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C97" s="6" t="inlineStr"/>
       <c r="D97" s="16">
-        <f>D85-D86</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E97" s="16">
-        <f>E85-E86</f>
+        <f>D88</f>
         <v/>
       </c>
       <c r="F97" s="16">
-        <f>F85-F86</f>
+        <f>E88</f>
         <v/>
       </c>
       <c r="G97" s="16">
-        <f>G85-G86</f>
+        <f>F88</f>
         <v/>
       </c>
       <c r="H97" s="16">
-        <f>H85-H86</f>
+        <f>G88</f>
         <v/>
       </c>
       <c r="I97" s="16">
-        <f>I85-I86</f>
+        <f>H88</f>
         <v/>
       </c>
       <c r="J97" s="16">
-        <f>J85-J86</f>
+        <f>I88</f>
         <v/>
       </c>
       <c r="K97" s="16">
-        <f>K85-K86</f>
+        <f>J88</f>
         <v/>
       </c>
       <c r="L97" s="16">
-        <f>L85-L86</f>
+        <f>K88</f>
         <v/>
       </c>
       <c r="M97" s="16">
-        <f>M85-M86</f>
+        <f>L88</f>
         <v/>
       </c>
       <c r="N97" s="16">
-        <f>N85-N86</f>
+        <f>M88</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D98" s="16">
+        <f>D85-D86</f>
+        <v/>
+      </c>
+      <c r="E98" s="16">
+        <f>E85-E86</f>
+        <v/>
+      </c>
+      <c r="F98" s="16">
+        <f>F85-F86</f>
+        <v/>
+      </c>
+      <c r="G98" s="16">
+        <f>G85-G86</f>
+        <v/>
+      </c>
+      <c r="H98" s="16">
+        <f>H85-H86</f>
+        <v/>
+      </c>
+      <c r="I98" s="16">
+        <f>I85-I86</f>
+        <v/>
+      </c>
+      <c r="J98" s="16">
+        <f>J85-J86</f>
+        <v/>
+      </c>
+      <c r="K98" s="16">
+        <f>K85-K86</f>
+        <v/>
+      </c>
+      <c r="L98" s="16">
+        <f>L85-L86</f>
+        <v/>
+      </c>
+      <c r="M98" s="16">
+        <f>M85-M86</f>
+        <v/>
+      </c>
+      <c r="N98" s="16">
+        <f>N85-N86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D98" s="16">
+      <c r="D99" s="16">
         <f>D86+D87</f>
         <v/>
       </c>
-      <c r="E98" s="16">
+      <c r="E99" s="16">
         <f>E86+E87</f>
         <v/>
       </c>
-      <c r="F98" s="16">
+      <c r="F99" s="16">
         <f>F86+F87</f>
         <v/>
       </c>
-      <c r="G98" s="16">
+      <c r="G99" s="16">
         <f>G86+G87</f>
         <v/>
       </c>
-      <c r="H98" s="16">
+      <c r="H99" s="16">
         <f>H86+H87</f>
         <v/>
       </c>
-      <c r="I98" s="16">
+      <c r="I99" s="16">
         <f>I86+I87</f>
         <v/>
       </c>
-      <c r="J98" s="16">
+      <c r="J99" s="16">
         <f>J86+J87</f>
         <v/>
       </c>
-      <c r="K98" s="16">
+      <c r="K99" s="16">
         <f>K86+K87</f>
         <v/>
       </c>
-      <c r="L98" s="16">
+      <c r="L99" s="16">
         <f>L86+L87</f>
         <v/>
       </c>
-      <c r="M98" s="16">
+      <c r="M99" s="16">
         <f>M86+M87</f>
         <v/>
       </c>
-      <c r="N98" s="16">
+      <c r="N99" s="16">
         <f>N86+N87</f>
         <v/>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUTION WATERFALL</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
-      <c r="J100" s="4" t="n"/>
-      <c r="K100" s="4" t="n"/>
-      <c r="L100" s="4" t="n"/>
-      <c r="M100" s="4" t="n"/>
-      <c r="N100" s="4" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>CFADS - DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E101" s="16">
-        <f>E73-E80-E87</f>
-        <v/>
-      </c>
-      <c r="F101" s="16">
-        <f>F73-F80-F87</f>
-        <v/>
-      </c>
-      <c r="G101" s="16">
-        <f>G73-G80-G87</f>
-        <v/>
-      </c>
-      <c r="H101" s="16">
-        <f>H73-H80-H87</f>
-        <v/>
-      </c>
-      <c r="I101" s="16">
-        <f>I73-I80-I87</f>
-        <v/>
-      </c>
-      <c r="J101" s="16">
-        <f>J73-J80-J87</f>
-        <v/>
-      </c>
-      <c r="K101" s="16">
-        <f>K73-K80-K87</f>
-        <v/>
-      </c>
-      <c r="L101" s="16">
-        <f>L73-L80-L87</f>
-        <v/>
-      </c>
-      <c r="M101" s="16">
-        <f>M73-M80-M87</f>
-        <v/>
-      </c>
-      <c r="N101" s="16">
-        <f>N73-N80-N87</f>
-        <v/>
-      </c>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="n"/>
+      <c r="J101" s="4" t="n"/>
+      <c r="K101" s="4" t="n"/>
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="4" t="n"/>
+      <c r="N101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr"/>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E102" s="19">
-        <f>IF(E82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F102" s="19">
-        <f>IF(F82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G102" s="19">
-        <f>IF(G82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H102" s="19">
-        <f>IF(H82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I102" s="19">
-        <f>IF(I82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J102" s="19">
-        <f>IF(J82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K102" s="19">
-        <f>IF(K82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L102" s="19">
-        <f>IF(L82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M102" s="19">
-        <f>IF(M82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N102" s="19">
-        <f>IF(N82&gt;=$D$46,"PASS","LOCKED")</f>
+          <t>CFADS - DS - DSRA Fund</t>
+        </is>
+      </c>
+      <c r="E102" s="16">
+        <f>E73-E80-E87</f>
+        <v/>
+      </c>
+      <c r="F102" s="16">
+        <f>F73-F80-F87</f>
+        <v/>
+      </c>
+      <c r="G102" s="16">
+        <f>G73-G80-G87</f>
+        <v/>
+      </c>
+      <c r="H102" s="16">
+        <f>H73-H80-H87</f>
+        <v/>
+      </c>
+      <c r="I102" s="16">
+        <f>I73-I80-I87</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>J73-J80-J87</f>
+        <v/>
+      </c>
+      <c r="K102" s="16">
+        <f>K73-K80-K87</f>
+        <v/>
+      </c>
+      <c r="L102" s="16">
+        <f>L73-L80-L87</f>
+        <v/>
+      </c>
+      <c r="M102" s="16">
+        <f>M73-M80-M87</f>
+        <v/>
+      </c>
+      <c r="N102" s="16">
+        <f>N73-N80-N87</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr"/>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E103" s="19">
+        <f>IF(E82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F103" s="19">
+        <f>IF(F82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G103" s="19">
+        <f>IF(G82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H103" s="19">
+        <f>IF(H82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I103" s="19">
+        <f>IF(I82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J103" s="19">
+        <f>IF(J82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K103" s="19">
+        <f>IF(K82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L103" s="19">
+        <f>IF(L82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M103" s="19">
+        <f>IF(M82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N103" s="19">
+        <f>IF(N82&gt;=$D$46,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t>Distributable Cash</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E103" s="7">
-        <f>IF(E92="PASS",MAX(0,E91),0)</f>
-        <v/>
-      </c>
-      <c r="F103" s="7">
-        <f>IF(F92="PASS",MAX(0,F91),0)</f>
-        <v/>
-      </c>
-      <c r="G103" s="7">
-        <f>IF(G92="PASS",MAX(0,G91),0)</f>
-        <v/>
-      </c>
-      <c r="H103" s="7">
-        <f>IF(H92="PASS",MAX(0,H91),0)</f>
-        <v/>
-      </c>
-      <c r="I103" s="7">
-        <f>IF(I92="PASS",MAX(0,I91),0)</f>
-        <v/>
-      </c>
-      <c r="J103" s="7">
-        <f>IF(J92="PASS",MAX(0,J91),0)</f>
-        <v/>
-      </c>
-      <c r="K103" s="7">
-        <f>IF(K92="PASS",MAX(0,K91),0)</f>
-        <v/>
-      </c>
-      <c r="L103" s="7">
-        <f>IF(L92="PASS",MAX(0,L91),0)</f>
-        <v/>
-      </c>
-      <c r="M103" s="7">
-        <f>IF(M92="PASS",MAX(0,M91),0)</f>
-        <v/>
-      </c>
-      <c r="N103" s="7">
-        <f>IF(N92="PASS",MAX(0,N91),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr"/>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr"/>
+      <c r="L104" s="7" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+      <c r="N104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>SOURCES &amp; USES (Year 0)</t>
         </is>
       </c>
-      <c r="B105" s="4" t="n"/>
-      <c r="C105" s="4" t="n"/>
-      <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="n"/>
-      <c r="F105" s="4" t="n"/>
-      <c r="G105" s="4" t="n"/>
-      <c r="H105" s="4" t="n"/>
-      <c r="I105" s="4" t="n"/>
-      <c r="J105" s="4" t="n"/>
-      <c r="K105" s="4" t="n"/>
-      <c r="L105" s="4" t="n"/>
-      <c r="M105" s="4" t="n"/>
-      <c r="N105" s="4" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="20" t="inlineStr">
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
+      <c r="K106" s="4" t="n"/>
+      <c r="L106" s="4" t="n"/>
+      <c r="M106" s="4" t="n"/>
+      <c r="N106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>USES</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr"/>
-      <c r="C106" s="6" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Purchase Price</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B107" s="6" t="inlineStr"/>
       <c r="C107" s="6" t="inlineStr"/>
-      <c r="D107" s="16">
-        <f>$D$17</f>
-        <v/>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  Purchase Price</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
@@ -5641,14 +5288,14 @@
       </c>
       <c r="C108" s="6" t="inlineStr"/>
       <c r="D108" s="16">
-        <f>$D$17*$D$18</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -5658,57 +5305,58 @@
       </c>
       <c r="C109" s="6" t="inlineStr"/>
       <c r="D109" s="16">
-        <f>D85</f>
+        <f>$D$17*$D$18</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  DSRA Funding</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr"/>
+      <c r="D110" s="16">
+        <f>D85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr"/>
-      <c r="D110" s="7">
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr"/>
+      <c r="D111" s="7">
         <f>D97+D98+D99</f>
         <v/>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr"/>
-      <c r="C112" s="6" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Debt</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B113" s="6" t="inlineStr"/>
       <c r="C113" s="6" t="inlineStr"/>
-      <c r="D113" s="16">
-        <f>$D$55</f>
-        <v/>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Pre-ITC Equity</t>
+          <t xml:space="preserve">  Debt</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -5716,20 +5364,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Uses - Debt</t>
-        </is>
-      </c>
+      <c r="C114" s="6" t="inlineStr"/>
       <c r="D114" s="16">
-        <f>D100-D103</f>
+        <f>$D$55</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ITC Benefit</t>
+          <t xml:space="preserve">  Pre-ITC Equity</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -5739,18 +5383,18 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Reduces equity required</t>
+          <t>Uses - Debt</t>
         </is>
       </c>
       <c r="D115" s="16">
-        <f>$D$56</f>
+        <f>D100-D103</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Equity</t>
+          <t xml:space="preserve">  ITC Benefit</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
@@ -5760,18 +5404,18 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Pre-ITC - ITC</t>
-        </is>
-      </c>
-      <c r="D116" s="7">
-        <f>D104-D105</f>
+          <t>Reduces equity required</t>
+        </is>
+      </c>
+      <c r="D116" s="16">
+        <f>$D$56</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
+          <t xml:space="preserve">  Net Equity</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -5779,70 +5423,71 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr"/>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Pre-ITC - ITC</t>
+        </is>
+      </c>
       <c r="D117" s="7">
-        <f>D103+D106+D105</f>
+        <f>D104-D105</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr"/>
+      <c r="D118" s="7">
+        <f>D103+D106+D105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
           <t>Balance Check</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr"/>
-      <c r="C118" s="6" t="inlineStr"/>
-      <c r="D118" s="10">
+      <c r="B119" s="6" t="inlineStr"/>
+      <c r="C119" s="6" t="inlineStr"/>
+      <c r="D119" s="10">
         <f>IF(ABS(D100-D107)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>EXIT CALCULATIONS</t>
         </is>
       </c>
-      <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="n"/>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
-      <c r="I120" s="4" t="n"/>
-      <c r="J120" s="4" t="n"/>
-      <c r="K120" s="4" t="n"/>
-      <c r="L120" s="4" t="n"/>
-      <c r="M120" s="4" t="n"/>
-      <c r="N120" s="4" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Exit EV</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="N121" s="16">
-        <f>$D$20*N68</f>
-        <v/>
-      </c>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
@@ -5852,18 +5497,15 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
-      </c>
-      <c r="N122" s="16">
-        <f>N81</f>
-        <v/>
-      </c>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="N122" s="16" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -5873,232 +5515,210 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
+          <t>Ending Bal at Exit</t>
         </is>
       </c>
       <c r="N123" s="16">
-        <f>N88</f>
+        <f>N81</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
+          <t>DSRA Release</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="N124" s="16">
+        <f>N88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>Exit Equity Proceeds</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
-      <c r="N124" s="7">
-        <f>N111-N112+N113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="N125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>EQUITY RETURNS</t>
         </is>
       </c>
-      <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="n"/>
-      <c r="D126" s="4" t="n"/>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="4" t="n"/>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="n"/>
-      <c r="I126" s="4" t="n"/>
-      <c r="J126" s="4" t="n"/>
-      <c r="K126" s="4" t="n"/>
-      <c r="L126" s="4" t="n"/>
-      <c r="M126" s="4" t="n"/>
-      <c r="N126" s="4" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Equity Cash Flow</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="16">
-        <f>-D106</f>
-        <v/>
-      </c>
-      <c r="E127" s="16">
-        <f>E93</f>
-        <v/>
-      </c>
-      <c r="F127" s="16">
-        <f>F93</f>
-        <v/>
-      </c>
-      <c r="G127" s="16">
-        <f>G93</f>
-        <v/>
-      </c>
-      <c r="H127" s="16">
-        <f>H93</f>
-        <v/>
-      </c>
-      <c r="I127" s="16">
-        <f>I93</f>
-        <v/>
-      </c>
-      <c r="J127" s="16">
-        <f>J93</f>
-        <v/>
-      </c>
-      <c r="K127" s="16">
-        <f>K93</f>
-        <v/>
-      </c>
-      <c r="L127" s="16">
-        <f>L93</f>
-        <v/>
-      </c>
-      <c r="M127" s="16">
-        <f>M93</f>
-        <v/>
-      </c>
-      <c r="N127" s="16">
-        <f>N93+N114</f>
-        <v/>
-      </c>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
+      <c r="K127" s="4" t="n"/>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
+      <c r="N127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>Equity Cash Flow</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="28">
-        <f>IRR(D117:N117)</f>
-        <v/>
-      </c>
+      <c r="D128" s="16" t="inlineStr"/>
+      <c r="E128" s="16" t="inlineStr"/>
+      <c r="F128" s="16" t="inlineStr"/>
+      <c r="G128" s="16" t="inlineStr"/>
+      <c r="H128" s="16" t="inlineStr"/>
+      <c r="I128" s="16" t="inlineStr"/>
+      <c r="J128" s="16" t="inlineStr"/>
+      <c r="K128" s="16" t="inlineStr"/>
+      <c r="L128" s="16" t="inlineStr"/>
+      <c r="M128" s="16" t="inlineStr"/>
+      <c r="N128" s="16" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr"/>
+      <c r="D129" s="28" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D129" s="27">
-        <f>SUMIF(D117:N117,"&gt;0")/ABS(D117)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20" t="inlineStr">
+      <c r="D130" s="27" t="inlineStr"/>
+    </row>
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
         <is>
           <t>Unlevered Returns (for reference)</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr"/>
-      <c r="C131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B132" s="6" t="inlineStr"/>
       <c r="C132" s="6" t="inlineStr"/>
-      <c r="D132" s="16">
-        <f>-$D$17-D98</f>
-        <v/>
-      </c>
-      <c r="E132" s="16">
-        <f>E73</f>
-        <v/>
-      </c>
-      <c r="F132" s="16">
-        <f>F73</f>
-        <v/>
-      </c>
-      <c r="G132" s="16">
-        <f>G73</f>
-        <v/>
-      </c>
-      <c r="H132" s="16">
-        <f>H73</f>
-        <v/>
-      </c>
-      <c r="I132" s="16">
-        <f>I73</f>
-        <v/>
-      </c>
-      <c r="J132" s="16">
-        <f>J73</f>
-        <v/>
-      </c>
-      <c r="K132" s="16">
-        <f>K73</f>
-        <v/>
-      </c>
-      <c r="L132" s="16">
-        <f>L73</f>
-        <v/>
-      </c>
-      <c r="M132" s="16">
-        <f>M73</f>
-        <v/>
-      </c>
-      <c r="N132" s="16">
-        <f>N73+N111</f>
-        <v/>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr"/>
+      <c r="D133" s="16">
+        <f>-$D$17-D98</f>
+        <v/>
+      </c>
+      <c r="E133" s="16">
+        <f>E73</f>
+        <v/>
+      </c>
+      <c r="F133" s="16">
+        <f>F73</f>
+        <v/>
+      </c>
+      <c r="G133" s="16">
+        <f>G73</f>
+        <v/>
+      </c>
+      <c r="H133" s="16">
+        <f>H73</f>
+        <v/>
+      </c>
+      <c r="I133" s="16">
+        <f>I73</f>
+        <v/>
+      </c>
+      <c r="J133" s="16">
+        <f>J73</f>
+        <v/>
+      </c>
+      <c r="K133" s="16">
+        <f>K73</f>
+        <v/>
+      </c>
+      <c r="L133" s="16">
+        <f>L73</f>
+        <v/>
+      </c>
+      <c r="M133" s="16">
+        <f>M73</f>
+        <v/>
+      </c>
+      <c r="N133" s="16">
+        <f>N73+N111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr"/>
-      <c r="D133" s="28">
-        <f>IRR(D122:N122)</f>
-        <v/>
-      </c>
+      <c r="C134" s="6" t="inlineStr"/>
+      <c r="D134" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,14 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -154,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -226,6 +234,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3043,7 +3053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3125,21 +3135,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
-        <is>
-          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
+      <c r="D3" s="7">
+        <f>$D$27</f>
+        <v/>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -3148,13 +3182,17 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="53" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Y1 EBITDA</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3162,218 +3200,241 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
       <c r="D4" s="7">
-        <f>$D$17</f>
-        <v/>
+        <f>E78</f>
+        <v/>
+      </c>
+      <c r="M4" s="54" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Y1 EBITDA</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="M5" s="54" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>═══════════ CONTROL PANEL ═══════════</t>
-        </is>
-      </c>
+      <c r="A6" s="46" t="n"/>
       <c r="B6" s="46" t="n"/>
       <c r="C6" s="46" t="n"/>
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="n"/>
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
       <c r="B7" s="46" t="n"/>
       <c r="C7" s="46" t="n"/>
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B8" s="46" t="n"/>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="46" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Revenue Mode</t>
+          <t>Contract End Year</t>
         </is>
       </c>
       <c r="B9" s="46" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>Contract End Year</t>
-        </is>
-      </c>
+      <c r="A10" s="46" t="n"/>
       <c r="B10" s="46" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>0 = pure merchant; else year PPA ends</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="n"/>
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
       <c r="B11" s="46" t="n"/>
       <c r="C11" s="46" t="n"/>
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t>TIMING</t>
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B12" s="46" t="n"/>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>Exit Year</t>
+          <t>Tax Credit End Year</t>
         </is>
       </c>
       <c r="B13" s="46" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 / 7 / 10</t>
+          <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
       <c r="D13" s="44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>Tax Credit End Year</t>
-        </is>
-      </c>
+      <c r="A14" s="46" t="n"/>
       <c r="B14" s="46" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>0 = N/A; else last year of PTC/ITC</t>
-        </is>
-      </c>
-      <c r="D14" s="44" t="n">
-        <v>0</v>
-      </c>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="n"/>
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
       <c r="B15" s="46" t="n"/>
       <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
+      <c r="D15" s="48" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>DEBT</t>
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B16" s="46" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="48" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Debt Sweep</t>
+          <t>Sweep %</t>
         </is>
       </c>
       <c r="B17" s="46" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>ON</t>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Sweep %</t>
-        </is>
-      </c>
+      <c r="A18" s="46" t="n"/>
       <c r="B18" s="46" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Active when Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="49" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="46" t="n"/>
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
       <c r="B19" s="46" t="n"/>
       <c r="C19" s="46" t="n"/>
-      <c r="D19" s="49" t="n"/>
+      <c r="D19" s="50" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>Exit Method</t>
         </is>
       </c>
       <c r="B20" s="46" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="50" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Multiple / DCF</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="inlineStr">
-        <is>
-          <t>Exit Method</t>
-        </is>
-      </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Multiple / DCF</t>
-        </is>
-      </c>
-      <c r="D21" s="44" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="10">
+        <f>D108</f>
+        <v/>
       </c>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
@@ -3387,52 +3448,81 @@
       <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Debt Payoff Y10</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="10">
-        <f>D108</f>
+        <f>IF(N81&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Debt Payoff Y10</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
+          <t>Min DSCR ≥ 1.30x</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
       <c r="D23" s="10">
-        <f>IF(N81&lt;1,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.30,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR ≥ 1.30x</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="10" t="n"/>
     </row>
     <row r="25"/>
-    <row r="26"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TRANSACTION INPUTS</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>TRANSACTION INPUTS</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>145</v>
+      </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
@@ -3447,27 +3537,27 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>145</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>ITC Rate</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -3477,83 +3567,98 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
+          <t>Investment Tax Credit</t>
         </is>
       </c>
       <c r="D29" s="29" t="n">
-        <v>0.015</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ITC Rate</t>
+          <t>Exit Multiple</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Investment Tax Credit</t>
-        </is>
-      </c>
-      <c r="D30" s="29" t="n">
-        <v>0.3</v>
+          <t>On exit year EBITDA</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>On exit year EBITDA</t>
-        </is>
-      </c>
-      <c r="D31" s="30" t="n">
-        <v>8</v>
+          <t>Hold period</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Hold period</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ASSET INPUTS</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>ASSET INPUTS</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>AC Capacity</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>MWac</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Inverter rating</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>115</v>
+      </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -3568,73 +3673,88 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AC Capacity</t>
+          <t>Capacity Factor</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>MWac</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Inverter rating</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>115</v>
+          <t>P50 estimate</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Capacity Factor</t>
+          <t>Degradation</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>P50 estimate</t>
+          <t>Annual output decline</t>
         </is>
       </c>
       <c r="D36" s="29" t="n">
-        <v>0.26</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Degradation</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Annual output decline</t>
-        </is>
-      </c>
-      <c r="D37" s="29" t="n">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="38"/>
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="29" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>PRICING INPUTS</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+    </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>PRICING INPUTS</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>PPA Price Y1</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Contracted price</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>35</v>
+      </c>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
@@ -3649,93 +3769,108 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PPA Price Y1</t>
+          <t>PPA Escalation</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Contracted price</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>35</v>
+          <t>Contract escalation</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PPA Escalation</t>
+          <t>BESS Revenue Y1</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Contract escalation</t>
-        </is>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>0.015</v>
+          <t>Arbitrage + ancillary</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>BESS Revenue Y1</t>
+          <t>BESS Revenue Escalation</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Arbitrage + ancillary</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>4.5</v>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>BESS Revenue Escalation</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Revenue growth</t>
-        </is>
-      </c>
-      <c r="D43" s="29" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="44"/>
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="29" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>COST INPUTS</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>COST INPUTS</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>O&amp;M Cost</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>$mm/yr</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Fixed operating costs</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
@@ -3750,93 +3885,108 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Cost</t>
+          <t>O&amp;M Escalation</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>$mm/yr</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Fixed operating costs</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>2</v>
+          <t>Cost escalation</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Escalation</t>
+          <t>Augmentation Year</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Cost escalation</t>
-        </is>
-      </c>
-      <c r="D47" s="29" t="n">
-        <v>0.02</v>
+          <t>BESS capacity augment</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Augmentation Year</t>
+          <t>Augmentation Cost</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>BESS capacity augment</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>7</v>
+          <t>Battery replacement</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Augmentation Cost</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Battery replacement</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50"/>
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>FINANCING INPUTS</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+    </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>FINANCING INPUTS</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Debt / Entry EV</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="n">
+        <v>0.35</v>
+      </c>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
@@ -3851,7 +4001,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Leverage</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3861,77 +4011,77 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Debt / Entry EV</t>
+          <t>Lower (contracted)</t>
         </is>
       </c>
       <c r="D52" s="29" t="n">
-        <v>0.35</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Lower (contracted)</t>
-        </is>
-      </c>
-      <c r="D53" s="29" t="n">
-        <v>0.055</v>
+          <t>Longer for contracted</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Longer for contracted</t>
+          <t>Debt service reserve</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Target DSCR</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>6</v>
+          <t>For sculpting</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Target DSCR</t>
+          <t>Lock-up DSCR</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3941,43 +4091,58 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>For sculpting</t>
+          <t>Distribution threshold</t>
         </is>
       </c>
       <c r="D56" s="30" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Lock-up DSCR</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Distribution threshold</t>
-        </is>
-      </c>
-      <c r="D57" s="30" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="58"/>
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="30" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TAX INPUTS</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+    </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>TAX INPUTS</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Blended federal + state</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
@@ -3992,73 +4157,89 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>MACRS Shield Years</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Blended federal + state</t>
-        </is>
-      </c>
-      <c r="D60" s="29" t="n">
-        <v>0.25</v>
+          <t>Years with no tax</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>MACRS Shield Years</t>
+          <t>Post-MACRS Tax Rate</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Years with no tax</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>6</v>
+          <t>Reduced effective rate</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Post-MACRS Tax Rate</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Reduced effective rate</t>
-        </is>
-      </c>
-      <c r="D62" s="29" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="63"/>
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="29" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATED ITEMS</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="n"/>
+    </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>CALCULATED ITEMS</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Y1 Generation</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>AC Cap × CF × 8760</t>
+        </is>
+      </c>
+      <c r="D64" s="15">
+        <f>$D$34*$D$35*8760</f>
+        <v/>
+      </c>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -4073,28 +4254,28 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Y1 Generation</t>
+          <t>Debt Amount</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>AC Cap × CF × 8760</t>
-        </is>
-      </c>
-      <c r="D65" s="15">
-        <f>$D$24*$D$25*8760</f>
+          <t>Entry EV × Leverage</t>
+        </is>
+      </c>
+      <c r="D65" s="16">
+        <f>$D$27*$D$51</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>ITC Benefit</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -4104,175 +4285,201 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
+          <t>Entry EV × ITC Rate</t>
         </is>
       </c>
       <c r="D66" s="16">
-        <f>$D$17*$D$41</f>
+        <f>$D$27*$D$29</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>ITC Benefit</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Entry EV × ITC Rate</t>
-        </is>
-      </c>
-      <c r="D67" s="16">
-        <f>$D$17*$D$19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68"/>
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="16" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING MODEL</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+    </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING MODEL</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>With degradation</t>
+        </is>
+      </c>
       <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
-      <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
+      <c r="E69" s="15">
+        <f>$D$64*(1-$D$36)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F69" s="15">
+        <f>$D$64*(1-$D$36)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G69" s="15">
+        <f>$D$64*(1-$D$36)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H69" s="15">
+        <f>$D$64*(1-$D$36)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I69" s="15">
+        <f>$D$64*(1-$D$36)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J69" s="15">
+        <f>$D$64*(1-$D$36)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K69" s="15">
+        <f>$D$64*(1-$D$36)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L69" s="15">
+        <f>$D$64*(1-$D$36)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M69" s="15">
+        <f>$D$64*(1-$D$36)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N69" s="15">
+        <f>$D$64*(1-$D$36)^(10-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Generation</t>
+          <t>PPA Price</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>With degradation</t>
-        </is>
-      </c>
-      <c r="E70" s="15">
-        <f>$D$54*(1-$D$26)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F70" s="15">
-        <f>$D$54*(1-$D$26)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G70" s="15">
-        <f>$D$54*(1-$D$26)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H70" s="15">
-        <f>$D$54*(1-$D$26)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I70" s="15">
-        <f>$D$54*(1-$D$26)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J70" s="15">
-        <f>$D$54*(1-$D$26)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K70" s="15">
-        <f>$D$54*(1-$D$26)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L70" s="15">
-        <f>$D$54*(1-$D$26)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M70" s="15">
-        <f>$D$54*(1-$D$26)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N70" s="15">
-        <f>$D$54*(1-$D$26)^(10-1)</f>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="E70" s="16">
+        <f>$D$39*(1+$D$40)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F70" s="16">
+        <f>$D$39*(1+$D$40)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G70" s="16">
+        <f>$D$39*(1+$D$40)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H70" s="16">
+        <f>$D$39*(1+$D$40)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I70" s="16">
+        <f>$D$39*(1+$D$40)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J70" s="16">
+        <f>$D$39*(1+$D$40)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K70" s="16">
+        <f>$D$39*(1+$D$40)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L70" s="16">
+        <f>$D$39*(1+$D$40)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M70" s="16">
+        <f>$D$39*(1+$D$40)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N70" s="16">
+        <f>$D$39*(1+$D$40)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>PPA Price</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E71" s="16">
-        <f>$D$29*(1+$D$30)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F71" s="16">
-        <f>$D$29*(1+$D$30)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G71" s="16">
-        <f>$D$29*(1+$D$30)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H71" s="16">
-        <f>$D$29*(1+$D$30)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I71" s="16">
-        <f>$D$29*(1+$D$30)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J71" s="16">
-        <f>$D$29*(1+$D$30)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K71" s="16">
-        <f>$D$29*(1+$D$30)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L71" s="16">
-        <f>$D$29*(1+$D$30)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M71" s="16">
-        <f>$D$29*(1+$D$30)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N71" s="16">
-        <f>$D$29*(1+$D$30)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72"/>
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="16" t="n"/>
+      <c r="G71" s="16" t="n"/>
+      <c r="H71" s="16" t="n"/>
+      <c r="I71" s="16" t="n"/>
+      <c r="J71" s="16" t="n"/>
+      <c r="K71" s="16" t="n"/>
+      <c r="L71" s="16" t="n"/>
+      <c r="M71" s="16" t="n"/>
+      <c r="N71" s="16" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>PPA Revenue</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Gen × PPA Price / 1M</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="16" t="n"/>
+      <c r="G72" s="16" t="n"/>
+      <c r="H72" s="16" t="n"/>
+      <c r="I72" s="16" t="n"/>
+      <c r="J72" s="16" t="n"/>
+      <c r="K72" s="16" t="n"/>
+      <c r="L72" s="16" t="n"/>
+      <c r="M72" s="16" t="n"/>
+      <c r="N72" s="16" t="n"/>
+    </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>PPA Revenue</t>
+          <t>BESS Revenue</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -4282,24 +4489,24 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Gen × PPA Price / 1M</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="inlineStr"/>
-      <c r="F73" s="16" t="inlineStr"/>
-      <c r="G73" s="16" t="inlineStr"/>
-      <c r="H73" s="16" t="inlineStr"/>
-      <c r="I73" s="16" t="inlineStr"/>
-      <c r="J73" s="16" t="inlineStr"/>
-      <c r="K73" s="16" t="inlineStr"/>
-      <c r="L73" s="16" t="inlineStr"/>
-      <c r="M73" s="16" t="inlineStr"/>
-      <c r="N73" s="16" t="inlineStr"/>
+          <t>Arbitrage + ancillary</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="n"/>
+      <c r="G73" s="16" t="n"/>
+      <c r="H73" s="16" t="n"/>
+      <c r="I73" s="16" t="n"/>
+      <c r="J73" s="16" t="n"/>
+      <c r="K73" s="16" t="n"/>
+      <c r="L73" s="16" t="n"/>
+      <c r="M73" s="16" t="n"/>
+      <c r="N73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>BESS Revenue</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -4307,152 +4514,169 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Arbitrage + ancillary</t>
-        </is>
-      </c>
-      <c r="E74" s="16" t="inlineStr"/>
-      <c r="F74" s="16" t="inlineStr"/>
-      <c r="G74" s="16" t="inlineStr"/>
-      <c r="H74" s="16" t="inlineStr"/>
-      <c r="I74" s="16" t="inlineStr"/>
-      <c r="J74" s="16" t="inlineStr"/>
-      <c r="K74" s="16" t="inlineStr"/>
-      <c r="L74" s="16" t="inlineStr"/>
-      <c r="M74" s="16" t="inlineStr"/>
-      <c r="N74" s="16" t="inlineStr"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="E74" s="17" t="n"/>
+      <c r="F74" s="17" t="n"/>
+      <c r="G74" s="17" t="n"/>
+      <c r="H74" s="17" t="n"/>
+      <c r="I74" s="17" t="n"/>
+      <c r="J74" s="17" t="n"/>
+      <c r="K74" s="17" t="n"/>
+      <c r="L74" s="17" t="n"/>
+      <c r="M74" s="17" t="n"/>
+      <c r="N74" s="17" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr"/>
-      <c r="E75" s="17" t="inlineStr"/>
-      <c r="F75" s="17" t="inlineStr"/>
-      <c r="G75" s="17" t="inlineStr"/>
-      <c r="H75" s="17" t="inlineStr"/>
-      <c r="I75" s="17" t="inlineStr"/>
-      <c r="J75" s="17" t="inlineStr"/>
-      <c r="K75" s="17" t="inlineStr"/>
-      <c r="L75" s="17" t="inlineStr"/>
-      <c r="M75" s="17" t="inlineStr"/>
-      <c r="N75" s="17" t="inlineStr"/>
-    </row>
-    <row r="76"/>
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="E75" s="17" t="n"/>
+      <c r="F75" s="17" t="n"/>
+      <c r="G75" s="17" t="n"/>
+      <c r="H75" s="17" t="n"/>
+      <c r="I75" s="17" t="n"/>
+      <c r="J75" s="17" t="n"/>
+      <c r="K75" s="17" t="n"/>
+      <c r="L75" s="17" t="n"/>
+      <c r="M75" s="17" t="n"/>
+      <c r="N75" s="17" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>O&amp;M Cost</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="n"/>
+      <c r="F76" s="16" t="n"/>
+      <c r="G76" s="16" t="n"/>
+      <c r="H76" s="16" t="n"/>
+      <c r="I76" s="16" t="n"/>
+      <c r="J76" s="16" t="n"/>
+      <c r="K76" s="16" t="n"/>
+      <c r="L76" s="16" t="n"/>
+      <c r="M76" s="16" t="n"/>
+      <c r="N76" s="16" t="n"/>
+    </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Cost</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E77" s="16">
-        <f>$D$35*(1+$D$36)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F77" s="16">
-        <f>$D$35*(1+$D$36)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G77" s="16">
-        <f>$D$35*(1+$D$36)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H77" s="16">
-        <f>$D$35*(1+$D$36)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I77" s="16">
-        <f>$D$35*(1+$D$36)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J77" s="16">
-        <f>$D$35*(1+$D$36)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K77" s="16">
-        <f>$D$35*(1+$D$36)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L77" s="16">
-        <f>$D$35*(1+$D$36)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M77" s="16">
-        <f>$D$35*(1+$D$36)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N77" s="16">
-        <f>$D$35*(1+$D$36)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78"/>
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="16" t="n"/>
+      <c r="G77" s="16" t="n"/>
+      <c r="H77" s="16" t="n"/>
+      <c r="I77" s="16" t="n"/>
+      <c r="J77" s="16" t="n"/>
+      <c r="K77" s="16" t="n"/>
+      <c r="L77" s="16" t="n"/>
+      <c r="M77" s="16" t="n"/>
+      <c r="N77" s="16" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
+      <c r="G78" s="7" t="n"/>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+      <c r="J78" s="7" t="n"/>
+      <c r="K78" s="7" t="n"/>
+      <c r="L78" s="7" t="n"/>
+      <c r="M78" s="7" t="n"/>
+      <c r="N78" s="7" t="n"/>
+    </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
-      <c r="K79" s="7" t="inlineStr"/>
-      <c r="L79" s="7" t="inlineStr"/>
-      <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
-    </row>
-    <row r="80"/>
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>CASH FLOW</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
+      <c r="I80" s="4" t="n"/>
+      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+    </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>MACRS shield Y1-Y6</t>
+        </is>
+      </c>
       <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="16" t="n"/>
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
+      <c r="I81" s="16" t="n"/>
+      <c r="J81" s="16" t="n"/>
+      <c r="K81" s="16" t="n"/>
+      <c r="L81" s="16" t="n"/>
+      <c r="M81" s="16" t="n"/>
+      <c r="N81" s="16" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>BESS Augmentation</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -4462,24 +4686,54 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>MACRS shield Y1-Y6</t>
-        </is>
-      </c>
-      <c r="E82" s="16" t="inlineStr"/>
-      <c r="F82" s="16" t="inlineStr"/>
-      <c r="G82" s="16" t="inlineStr"/>
-      <c r="H82" s="16" t="inlineStr"/>
-      <c r="I82" s="16" t="inlineStr"/>
-      <c r="J82" s="16" t="inlineStr"/>
-      <c r="K82" s="16" t="inlineStr"/>
-      <c r="L82" s="16" t="inlineStr"/>
-      <c r="M82" s="16" t="inlineStr"/>
-      <c r="N82" s="16" t="inlineStr"/>
+          <t>Battery replacement</t>
+        </is>
+      </c>
+      <c r="E82" s="18">
+        <f>IF(1=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="F82" s="18">
+        <f>IF(2=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="G82" s="18">
+        <f>IF(3=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="H82" s="18">
+        <f>IF(4=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="I82" s="18">
+        <f>IF(5=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="18">
+        <f>IF(6=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="K82" s="18">
+        <f>IF(7=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="L82" s="18">
+        <f>IF(8=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="M82" s="18">
+        <f>IF(9=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
+      <c r="N82" s="18">
+        <f>IF(10=$D$47,$D$48,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>BESS Augmentation</t>
+          <t>CFADS</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -4489,102 +4743,119 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Battery replacement</t>
-        </is>
-      </c>
-      <c r="E83" s="18">
-        <f>IF(1=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="F83" s="18">
-        <f>IF(2=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="G83" s="18">
-        <f>IF(3=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="H83" s="18">
-        <f>IF(4=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="I83" s="18">
-        <f>IF(5=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="J83" s="18">
-        <f>IF(6=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="K83" s="18">
-        <f>IF(7=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="L83" s="18">
-        <f>IF(8=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="M83" s="18">
-        <f>IF(9=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
-      <c r="N83" s="18">
-        <f>IF(10=$D$37,$D$38,0)</f>
-        <v/>
-      </c>
+          <t>EBITDA - Taxes - Augment</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="7" t="n"/>
+      <c r="G83" s="7" t="n"/>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
+      <c r="J83" s="7" t="n"/>
+      <c r="K83" s="7" t="n"/>
+      <c r="L83" s="7" t="n"/>
+      <c r="M83" s="7" t="n"/>
+      <c r="N83" s="7" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Taxes - Augment</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr"/>
-      <c r="F84" s="7" t="inlineStr"/>
-      <c r="G84" s="7" t="inlineStr"/>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="7" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr"/>
-      <c r="L84" s="7" t="inlineStr"/>
-      <c r="M84" s="7" t="inlineStr"/>
-      <c r="N84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85"/>
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="7" t="n"/>
+      <c r="G84" s="7" t="n"/>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
+      <c r="J84" s="7" t="n"/>
+      <c r="K84" s="7" t="n"/>
+      <c r="L84" s="7" t="n"/>
+      <c r="M84" s="7" t="n"/>
+      <c r="N84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SCHEDULE (Sculpted to 1.35x DSCR)</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+    </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SCHEDULE (Sculpted to 1.35x DSCR)</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
-      <c r="J86" s="4" t="n"/>
-      <c r="K86" s="4" t="n"/>
-      <c r="L86" s="4" t="n"/>
-      <c r="M86" s="4" t="n"/>
-      <c r="N86" s="4" t="n"/>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="16">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="F86" s="16">
+        <f>E91</f>
+        <v/>
+      </c>
+      <c r="G86" s="16">
+        <f>F91</f>
+        <v/>
+      </c>
+      <c r="H86" s="16">
+        <f>G91</f>
+        <v/>
+      </c>
+      <c r="I86" s="16">
+        <f>H91</f>
+        <v/>
+      </c>
+      <c r="J86" s="16">
+        <f>I91</f>
+        <v/>
+      </c>
+      <c r="K86" s="16">
+        <f>J91</f>
+        <v/>
+      </c>
+      <c r="L86" s="16">
+        <f>K91</f>
+        <v/>
+      </c>
+      <c r="M86" s="16">
+        <f>L91</f>
+        <v/>
+      </c>
+      <c r="N86" s="16">
+        <f>M91</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Beginning Balance</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -4592,52 +4863,26 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr"/>
-      <c r="E87" s="16">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="F87" s="16">
-        <f>E81</f>
-        <v/>
-      </c>
-      <c r="G87" s="16">
-        <f>F81</f>
-        <v/>
-      </c>
-      <c r="H87" s="16">
-        <f>G81</f>
-        <v/>
-      </c>
-      <c r="I87" s="16">
-        <f>H81</f>
-        <v/>
-      </c>
-      <c r="J87" s="16">
-        <f>I81</f>
-        <v/>
-      </c>
-      <c r="K87" s="16">
-        <f>J81</f>
-        <v/>
-      </c>
-      <c r="L87" s="16">
-        <f>K81</f>
-        <v/>
-      </c>
-      <c r="M87" s="16">
-        <f>L81</f>
-        <v/>
-      </c>
-      <c r="N87" s="16">
-        <f>M81</f>
-        <v/>
-      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="16" t="n"/>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
+      <c r="I87" s="16" t="n"/>
+      <c r="J87" s="16" t="n"/>
+      <c r="K87" s="16" t="n"/>
+      <c r="L87" s="16" t="n"/>
+      <c r="M87" s="16" t="n"/>
+      <c r="N87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Target Debt Service</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -4647,24 +4892,24 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="inlineStr"/>
-      <c r="F88" s="16" t="inlineStr"/>
-      <c r="G88" s="16" t="inlineStr"/>
-      <c r="H88" s="16" t="inlineStr"/>
-      <c r="I88" s="16" t="inlineStr"/>
-      <c r="J88" s="16" t="inlineStr"/>
-      <c r="K88" s="16" t="inlineStr"/>
-      <c r="L88" s="16" t="inlineStr"/>
-      <c r="M88" s="16" t="inlineStr"/>
-      <c r="N88" s="16" t="inlineStr"/>
+          <t>CFADS / Target DSCR</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="n"/>
+      <c r="F88" s="16" t="n"/>
+      <c r="G88" s="16" t="n"/>
+      <c r="H88" s="16" t="n"/>
+      <c r="I88" s="16" t="n"/>
+      <c r="J88" s="16" t="n"/>
+      <c r="K88" s="16" t="n"/>
+      <c r="L88" s="16" t="n"/>
+      <c r="M88" s="16" t="n"/>
+      <c r="N88" s="16" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Target Debt Service</t>
+          <t>Sculpted Principal</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4674,24 +4919,24 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Target DSCR</t>
-        </is>
-      </c>
-      <c r="E89" s="16" t="inlineStr"/>
-      <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr"/>
-      <c r="H89" s="16" t="inlineStr"/>
-      <c r="I89" s="16" t="inlineStr"/>
-      <c r="J89" s="16" t="inlineStr"/>
-      <c r="K89" s="16" t="inlineStr"/>
-      <c r="L89" s="16" t="inlineStr"/>
-      <c r="M89" s="16" t="inlineStr"/>
-      <c r="N89" s="16" t="inlineStr"/>
+          <t>Target DS - Interest</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="16" t="n"/>
+      <c r="H89" s="16" t="n"/>
+      <c r="I89" s="16" t="n"/>
+      <c r="J89" s="16" t="n"/>
+      <c r="K89" s="16" t="n"/>
+      <c r="L89" s="16" t="n"/>
+      <c r="M89" s="16" t="n"/>
+      <c r="N89" s="16" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Sculpted Principal</t>
+          <t>Actual Debt Service</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -4701,24 +4946,24 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Target DS - Interest</t>
-        </is>
-      </c>
-      <c r="E90" s="16" t="inlineStr"/>
-      <c r="F90" s="16" t="inlineStr"/>
-      <c r="G90" s="16" t="inlineStr"/>
-      <c r="H90" s="16" t="inlineStr"/>
-      <c r="I90" s="16" t="inlineStr"/>
-      <c r="J90" s="16" t="inlineStr"/>
-      <c r="K90" s="16" t="inlineStr"/>
-      <c r="L90" s="16" t="inlineStr"/>
-      <c r="M90" s="16" t="inlineStr"/>
-      <c r="N90" s="16" t="inlineStr"/>
+          <t>Interest + Principal</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="16" t="n"/>
+      <c r="G90" s="16" t="n"/>
+      <c r="H90" s="16" t="n"/>
+      <c r="I90" s="16" t="n"/>
+      <c r="J90" s="16" t="n"/>
+      <c r="K90" s="16" t="n"/>
+      <c r="L90" s="16" t="n"/>
+      <c r="M90" s="16" t="n"/>
+      <c r="N90" s="16" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Actual Debt Service</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4728,129 +4973,150 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Interest + Principal</t>
-        </is>
-      </c>
-      <c r="E91" s="16">
-        <f>E77+E79</f>
-        <v/>
-      </c>
-      <c r="F91" s="16">
-        <f>F77+F79</f>
-        <v/>
-      </c>
-      <c r="G91" s="16">
-        <f>G77+G79</f>
-        <v/>
-      </c>
-      <c r="H91" s="16">
-        <f>H77+H79</f>
-        <v/>
-      </c>
-      <c r="I91" s="16">
-        <f>I77+I79</f>
-        <v/>
-      </c>
-      <c r="J91" s="16">
-        <f>J77+J79</f>
-        <v/>
-      </c>
-      <c r="K91" s="16">
-        <f>K77+K79</f>
-        <v/>
-      </c>
-      <c r="L91" s="16">
-        <f>L77+L79</f>
-        <v/>
-      </c>
-      <c r="M91" s="16">
-        <f>M77+M79</f>
-        <v/>
-      </c>
-      <c r="N91" s="16">
-        <f>N77+N79</f>
-        <v/>
-      </c>
+          <t>Beg - Principal</t>
+        </is>
+      </c>
+      <c r="D91">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="E91" s="16" t="n"/>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="16" t="n"/>
+      <c r="J91" s="16" t="n"/>
+      <c r="K91" s="16" t="n"/>
+      <c r="L91" s="16" t="n"/>
+      <c r="M91" s="16" t="n"/>
+      <c r="N91" s="16" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Actual DSCR</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Beg - Principal</t>
-        </is>
-      </c>
-      <c r="E92" s="16" t="inlineStr"/>
-      <c r="F92" s="16" t="inlineStr"/>
-      <c r="G92" s="16" t="inlineStr"/>
-      <c r="H92" s="16" t="inlineStr"/>
-      <c r="I92" s="16" t="inlineStr"/>
-      <c r="J92" s="16" t="inlineStr"/>
-      <c r="K92" s="16" t="inlineStr"/>
-      <c r="L92" s="16" t="inlineStr"/>
-      <c r="M92" s="16" t="inlineStr"/>
-      <c r="N92" s="16" t="inlineStr"/>
+          <t>CFADS / Actual DS</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="27" t="n"/>
+      <c r="H92" s="27" t="n"/>
+      <c r="I92" s="27" t="n"/>
+      <c r="J92" s="27" t="n"/>
+      <c r="K92" s="27" t="n"/>
+      <c r="L92" s="27" t="n"/>
+      <c r="M92" s="27" t="n"/>
+      <c r="N92" s="27" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Actual DSCR</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Actual DS</t>
-        </is>
-      </c>
-      <c r="E93" s="27" t="inlineStr"/>
-      <c r="F93" s="27" t="inlineStr"/>
-      <c r="G93" s="27" t="inlineStr"/>
-      <c r="H93" s="27" t="inlineStr"/>
-      <c r="I93" s="27" t="inlineStr"/>
-      <c r="J93" s="27" t="inlineStr"/>
-      <c r="K93" s="27" t="inlineStr"/>
-      <c r="L93" s="27" t="inlineStr"/>
-      <c r="M93" s="27" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr"/>
-    </row>
-    <row r="94"/>
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="E93" s="27" t="n"/>
+      <c r="F93" s="27" t="n"/>
+      <c r="G93" s="27" t="n"/>
+      <c r="H93" s="27" t="n"/>
+      <c r="I93" s="27" t="n"/>
+      <c r="J93" s="27" t="n"/>
+      <c r="K93" s="27" t="n"/>
+      <c r="L93" s="27" t="n"/>
+      <c r="M93" s="27" t="n"/>
+      <c r="N93" s="27" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>DSRA (Debt Service Reserve Account)</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="4" t="n"/>
+    </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>DSRA (Debt Service Reserve Account)</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
-      <c r="K95" s="4" t="n"/>
-      <c r="L95" s="4" t="n"/>
-      <c r="M95" s="4" t="n"/>
-      <c r="N95" s="4" t="n"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>DSRA Target</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr DS × DSRA Months / 12</t>
+        </is>
+      </c>
+      <c r="D95" s="16">
+        <f>E80*$D$44/12</f>
+        <v/>
+      </c>
+      <c r="E95" s="16">
+        <f>F90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="F95" s="16">
+        <f>G90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="G95" s="16">
+        <f>H90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="H95" s="16">
+        <f>I90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="I95" s="16">
+        <f>J90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="J95" s="16">
+        <f>K90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="K95" s="16">
+        <f>L90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="L95" s="16">
+        <f>M90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="M95" s="16">
+        <f>N90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="N95" s="16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>DSRA Target</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -4858,60 +5124,55 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D96" s="16">
-        <f>E80*$D$44/12</f>
-        <v/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E96" s="16">
-        <f>F80*$D$44/12</f>
+        <f>D109</f>
         <v/>
       </c>
       <c r="F96" s="16">
-        <f>G80*$D$44/12</f>
+        <f>E98</f>
         <v/>
       </c>
       <c r="G96" s="16">
-        <f>H80*$D$44/12</f>
+        <f>F98</f>
         <v/>
       </c>
       <c r="H96" s="16">
-        <f>I80*$D$44/12</f>
+        <f>G98</f>
         <v/>
       </c>
       <c r="I96" s="16">
-        <f>J80*$D$44/12</f>
+        <f>H98</f>
         <v/>
       </c>
       <c r="J96" s="16">
-        <f>K80*$D$44/12</f>
+        <f>I98</f>
         <v/>
       </c>
       <c r="K96" s="16">
-        <f>L80*$D$44/12</f>
+        <f>J98</f>
         <v/>
       </c>
       <c r="L96" s="16">
-        <f>M80*$D$44/12</f>
+        <f>K98</f>
         <v/>
       </c>
       <c r="M96" s="16">
-        <f>N80*$D$44/12</f>
+        <f>L98</f>
         <v/>
       </c>
       <c r="N96" s="16">
-        <f>0</f>
+        <f>M98</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Funding/(Release)</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -4919,56 +5180,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr"/>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
       <c r="D97" s="16">
-        <f>0</f>
+        <f>D85-D86</f>
         <v/>
       </c>
       <c r="E97" s="16">
-        <f>D88</f>
+        <f>E95-E96</f>
         <v/>
       </c>
       <c r="F97" s="16">
-        <f>E88</f>
+        <f>F95-F96</f>
         <v/>
       </c>
       <c r="G97" s="16">
-        <f>F88</f>
+        <f>G95-G96</f>
         <v/>
       </c>
       <c r="H97" s="16">
-        <f>G88</f>
+        <f>H95-H96</f>
         <v/>
       </c>
       <c r="I97" s="16">
-        <f>H88</f>
+        <f>I95-I96</f>
         <v/>
       </c>
       <c r="J97" s="16">
-        <f>I88</f>
+        <f>J95-J96</f>
         <v/>
       </c>
       <c r="K97" s="16">
-        <f>J88</f>
+        <f>K95-K96</f>
         <v/>
       </c>
       <c r="L97" s="16">
-        <f>K88</f>
+        <f>L95-L96</f>
         <v/>
       </c>
       <c r="M97" s="16">
-        <f>L88</f>
+        <f>M95-M96</f>
         <v/>
       </c>
       <c r="N97" s="16">
-        <f>M88</f>
+        <f>N95-N96</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Ending</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -4978,282 +5243,301 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Target - Beginning</t>
+          <t>Beginning + Funding</t>
         </is>
       </c>
       <c r="D98" s="16">
-        <f>D85-D86</f>
+        <f>D86+D87</f>
         <v/>
       </c>
       <c r="E98" s="16">
-        <f>E85-E86</f>
+        <f>E96+E97</f>
         <v/>
       </c>
       <c r="F98" s="16">
-        <f>F85-F86</f>
+        <f>F96+F97</f>
         <v/>
       </c>
       <c r="G98" s="16">
-        <f>G85-G86</f>
+        <f>G96+G97</f>
         <v/>
       </c>
       <c r="H98" s="16">
-        <f>H85-H86</f>
+        <f>H96+H97</f>
         <v/>
       </c>
       <c r="I98" s="16">
-        <f>I85-I86</f>
+        <f>I96+I97</f>
         <v/>
       </c>
       <c r="J98" s="16">
-        <f>J85-J86</f>
+        <f>J96+J97</f>
         <v/>
       </c>
       <c r="K98" s="16">
-        <f>K85-K86</f>
+        <f>K96+K97</f>
         <v/>
       </c>
       <c r="L98" s="16">
-        <f>L85-L86</f>
+        <f>L96+L97</f>
         <v/>
       </c>
       <c r="M98" s="16">
-        <f>M85-M86</f>
+        <f>M96+M97</f>
         <v/>
       </c>
       <c r="N98" s="16">
-        <f>N85-N86</f>
+        <f>N96+N97</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Ending</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>Beginning + Funding</t>
-        </is>
-      </c>
-      <c r="D99" s="16">
-        <f>D86+D87</f>
-        <v/>
-      </c>
-      <c r="E99" s="16">
-        <f>E86+E87</f>
-        <v/>
-      </c>
-      <c r="F99" s="16">
-        <f>F86+F87</f>
-        <v/>
-      </c>
-      <c r="G99" s="16">
-        <f>G86+G87</f>
-        <v/>
-      </c>
-      <c r="H99" s="16">
-        <f>H86+H87</f>
-        <v/>
-      </c>
-      <c r="I99" s="16">
-        <f>I86+I87</f>
-        <v/>
-      </c>
-      <c r="J99" s="16">
-        <f>J86+J87</f>
-        <v/>
-      </c>
-      <c r="K99" s="16">
-        <f>K86+K87</f>
-        <v/>
-      </c>
-      <c r="L99" s="16">
-        <f>L86+L87</f>
-        <v/>
-      </c>
-      <c r="M99" s="16">
-        <f>M86+M87</f>
-        <v/>
-      </c>
-      <c r="N99" s="16">
-        <f>N86+N87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100"/>
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="6" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="16" t="n"/>
+      <c r="E99" s="16" t="n"/>
+      <c r="F99" s="16" t="n"/>
+      <c r="G99" s="16" t="n"/>
+      <c r="H99" s="16" t="n"/>
+      <c r="I99" s="16" t="n"/>
+      <c r="J99" s="16" t="n"/>
+      <c r="K99" s="16" t="n"/>
+      <c r="L99" s="16" t="n"/>
+      <c r="M99" s="16" t="n"/>
+      <c r="N99" s="16" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION WATERFALL</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4" t="n"/>
+    </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION WATERFALL</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="n"/>
-      <c r="C101" s="4" t="n"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>CFADS - DS - DSRA Fund</t>
+        </is>
+      </c>
       <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="n"/>
-      <c r="J101" s="4" t="n"/>
-      <c r="K101" s="4" t="n"/>
-      <c r="L101" s="4" t="n"/>
-      <c r="M101" s="4" t="n"/>
-      <c r="N101" s="4" t="n"/>
+      <c r="E101" s="16">
+        <f>E83-E90-E97</f>
+        <v/>
+      </c>
+      <c r="F101" s="16">
+        <f>F83-F90-F97</f>
+        <v/>
+      </c>
+      <c r="G101" s="16">
+        <f>G83-G90-G97</f>
+        <v/>
+      </c>
+      <c r="H101" s="16">
+        <f>H83-H90-H97</f>
+        <v/>
+      </c>
+      <c r="I101" s="16">
+        <f>I83-I90-I97</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>J83-J90-J97</f>
+        <v/>
+      </c>
+      <c r="K101" s="16">
+        <f>K83-K90-K97</f>
+        <v/>
+      </c>
+      <c r="L101" s="16">
+        <f>L83-L90-L97</f>
+        <v/>
+      </c>
+      <c r="M101" s="16">
+        <f>M83-M90-M97</f>
+        <v/>
+      </c>
+      <c r="N101" s="16">
+        <f>N83-N90-N97</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n"/>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E102" s="16">
-        <f>E73-E80-E87</f>
-        <v/>
-      </c>
-      <c r="F102" s="16">
-        <f>F73-F80-F87</f>
-        <v/>
-      </c>
-      <c r="G102" s="16">
-        <f>G73-G80-G87</f>
-        <v/>
-      </c>
-      <c r="H102" s="16">
-        <f>H73-H80-H87</f>
-        <v/>
-      </c>
-      <c r="I102" s="16">
-        <f>I73-I80-I87</f>
-        <v/>
-      </c>
-      <c r="J102" s="16">
-        <f>J73-J80-J87</f>
-        <v/>
-      </c>
-      <c r="K102" s="16">
-        <f>K73-K80-K87</f>
-        <v/>
-      </c>
-      <c r="L102" s="16">
-        <f>L73-L80-L87</f>
-        <v/>
-      </c>
-      <c r="M102" s="16">
-        <f>M73-M80-M87</f>
-        <v/>
-      </c>
-      <c r="N102" s="16">
-        <f>N73-N80-N87</f>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E102" s="19">
+        <f>IF(E92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F102" s="19">
+        <f>IF(F92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G102" s="19">
+        <f>IF(G92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H102" s="19">
+        <f>IF(H92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I102" s="19">
+        <f>IF(I92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J102" s="19">
+        <f>IF(J92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K102" s="19">
+        <f>IF(K92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L102" s="19">
+        <f>IF(L92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M102" s="19">
+        <f>IF(M92&gt;=$D$56,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N102" s="19">
+        <f>IF(N92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr"/>
+          <t>Distributable Cash</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E103" s="19">
-        <f>IF(E82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F103" s="19">
-        <f>IF(F82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G103" s="19">
-        <f>IF(G82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H103" s="19">
-        <f>IF(H82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I103" s="19">
-        <f>IF(I82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J103" s="19">
-        <f>IF(J82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K103" s="19">
-        <f>IF(K82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L103" s="19">
-        <f>IF(L82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M103" s="19">
-        <f>IF(M82&gt;=$D$46,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N103" s="19">
-        <f>IF(N82&gt;=$D$46,"PASS","LOCKED")</f>
+          <t>If PASS, MAX(0, Cash Avail)</t>
+        </is>
+      </c>
+      <c r="E103" s="7">
+        <f>IF(E102="PASS",MAX(0,E101),0)</f>
+        <v/>
+      </c>
+      <c r="F103" s="7">
+        <f>IF(F102="PASS",MAX(0,F101),0)</f>
+        <v/>
+      </c>
+      <c r="G103" s="7">
+        <f>IF(G102="PASS",MAX(0,G101),0)</f>
+        <v/>
+      </c>
+      <c r="H103" s="7">
+        <f>IF(H102="PASS",MAX(0,H101),0)</f>
+        <v/>
+      </c>
+      <c r="I103" s="7">
+        <f>IF(I102="PASS",MAX(0,I101),0)</f>
+        <v/>
+      </c>
+      <c r="J103" s="7">
+        <f>IF(J102="PASS",MAX(0,J101),0)</f>
+        <v/>
+      </c>
+      <c r="K103" s="7">
+        <f>IF(K102="PASS",MAX(0,K101),0)</f>
+        <v/>
+      </c>
+      <c r="L103" s="7">
+        <f>IF(L102="PASS",MAX(0,L101),0)</f>
+        <v/>
+      </c>
+      <c r="M103" s="7">
+        <f>IF(M102="PASS",MAX(0,M101),0)</f>
+        <v/>
+      </c>
+      <c r="N103" s="7">
+        <f>IF(N102="PASS",MAX(0,N101),0)</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Distributable Cash</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>If PASS, MAX(0, Cash Avail)</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr"/>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="7" t="inlineStr"/>
-      <c r="J104" s="7" t="inlineStr"/>
-      <c r="K104" s="7" t="inlineStr"/>
-      <c r="L104" s="7" t="inlineStr"/>
-      <c r="M104" s="7" t="inlineStr"/>
-      <c r="N104" s="7" t="inlineStr"/>
-    </row>
-    <row r="105"/>
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="E104" s="7" t="n"/>
+      <c r="F104" s="7" t="n"/>
+      <c r="G104" s="7" t="n"/>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
+      <c r="J104" s="7" t="n"/>
+      <c r="K104" s="7" t="n"/>
+      <c r="L104" s="7" t="n"/>
+      <c r="M104" s="7" t="n"/>
+      <c r="N104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; USES (Year 0)</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="4" t="n"/>
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="n"/>
+      <c r="L105" s="4" t="n"/>
+      <c r="M105" s="4" t="n"/>
+      <c r="N105" s="4" t="n"/>
+    </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; USES (Year 0)</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>USES</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
       <c r="D106" s="4" t="n"/>
       <c r="E106" s="4" t="n"/>
       <c r="F106" s="4" t="n"/>
@@ -5267,18 +5551,26 @@
       <c r="N106" s="4" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>USES</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr"/>
-      <c r="C107" s="6" t="inlineStr"/>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Purchase Price</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="16">
+        <f>$D$27</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase Price</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
@@ -5286,16 +5578,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr"/>
+      <c r="C108" s="6" t="n"/>
       <c r="D108" s="16">
-        <f>$D$17</f>
+        <f>$D$27*$D$28</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  DSRA Funding</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -5303,16 +5595,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr"/>
+      <c r="C109" s="6" t="n"/>
       <c r="D109" s="16">
-        <f>$D$17*$D$18</f>
+        <f>E95</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t>Total Uses</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -5320,43 +5612,48 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr"/>
-      <c r="D110" s="16">
-        <f>D85</f>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="7">
+        <f>D107+D108+D109</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr"/>
-      <c r="D111" s="7">
-        <f>D97+D98+D99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112"/>
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="6" t="n"/>
+    </row>
     <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr"/>
-      <c r="C113" s="6" t="inlineStr"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Debt</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="16">
+        <f>$D$27*$D$51</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Debt</t>
+          <t xml:space="preserve">  Pre-ITC Equity</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -5364,16 +5661,20 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr"/>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Uses - Debt</t>
+        </is>
+      </c>
       <c r="D114" s="16">
-        <f>$D$55</f>
+        <f>D110-D113</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Pre-ITC Equity</t>
+          <t xml:space="preserve">  ITC Benefit</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -5383,18 +5684,18 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Uses - Debt</t>
+          <t>Reduces equity required</t>
         </is>
       </c>
       <c r="D115" s="16">
-        <f>D100-D103</f>
+        <f>$D$66</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ITC Benefit</t>
+          <t xml:space="preserve">  Net Equity</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
@@ -5404,18 +5705,18 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Reduces equity required</t>
-        </is>
-      </c>
-      <c r="D116" s="16">
-        <f>$D$56</f>
+          <t>Pre-ITC - ITC</t>
+        </is>
+      </c>
+      <c r="D116" s="7">
+        <f>D114-D115</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Equity</t>
+          <t>Total Sources</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -5423,56 +5724,71 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Pre-ITC - ITC</t>
-        </is>
-      </c>
+      <c r="C117" s="6" t="n"/>
       <c r="D117" s="7">
-        <f>D104-D105</f>
+        <f>D113+D116+D115</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr"/>
-      <c r="D118" s="7">
-        <f>D103+D106+D105</f>
+          <t>Balance Check</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="10">
+        <f>IF(ABS(D110-D117)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Balance Check</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr"/>
-      <c r="C119" s="6" t="inlineStr"/>
-      <c r="D119" s="10">
-        <f>IF(ABS(D100-D107)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120"/>
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="6" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>EXIT CALCULATIONS</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
+      <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+    </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>EXIT CALCULATIONS</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="n"/>
-      <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="n"/>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Exit EV</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="D121" s="4">
+        <f>N78*$D$30</f>
+        <v/>
+      </c>
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="4" t="n"/>
@@ -5482,12 +5798,15 @@
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
-      <c r="N121" s="4" t="n"/>
+      <c r="N121" s="16">
+        <f>$D$20*N68</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Exit EV</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
@@ -5497,15 +5816,22 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="N122" s="16" t="inlineStr"/>
+          <t>Ending Bal at Exit</t>
+        </is>
+      </c>
+      <c r="D122">
+        <f>N91</f>
+        <v/>
+      </c>
+      <c r="N122" s="16">
+        <f>N81</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>DSRA Release</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -5515,18 +5841,22 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="D123">
+        <f>N98</f>
+        <v/>
       </c>
       <c r="N123" s="16">
-        <f>N81</f>
+        <f>N88</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
@@ -5536,190 +5866,282 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
-        </is>
-      </c>
-      <c r="N124" s="16">
-        <f>N88</f>
+          <t>Exit EV - Debt + DSRA</t>
+        </is>
+      </c>
+      <c r="D124">
+        <f>D121-D122+D123</f>
+        <v/>
+      </c>
+      <c r="N124" s="7">
+        <f>N111-N112+N113</f>
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Exit Equity Proceeds</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>Exit EV - Debt + DSRA</t>
-        </is>
-      </c>
-      <c r="N125" s="7" t="inlineStr"/>
-    </row>
-    <row r="126"/>
+      <c r="A125" s="5" t="n"/>
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="N125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY RETURNS</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n"/>
+      <c r="C126" s="4" t="n"/>
+      <c r="D126" s="4" t="n"/>
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="n"/>
+      <c r="G126" s="4" t="n"/>
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="4" t="n"/>
+      <c r="J126" s="4" t="n"/>
+      <c r="K126" s="4" t="n"/>
+      <c r="L126" s="4" t="n"/>
+      <c r="M126" s="4" t="n"/>
+      <c r="N126" s="4" t="n"/>
+    </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>EQUITY RETURNS</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="n"/>
-      <c r="C127" s="4" t="n"/>
-      <c r="D127" s="4" t="n"/>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="n"/>
-      <c r="G127" s="4" t="n"/>
-      <c r="H127" s="4" t="n"/>
-      <c r="I127" s="4" t="n"/>
-      <c r="J127" s="4" t="n"/>
-      <c r="K127" s="4" t="n"/>
-      <c r="L127" s="4" t="n"/>
-      <c r="M127" s="4" t="n"/>
-      <c r="N127" s="4" t="n"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Equity Cash Flow</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="16">
+        <f>-D116</f>
+        <v/>
+      </c>
+      <c r="E127" s="16">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="F127" s="16">
+        <f>F103</f>
+        <v/>
+      </c>
+      <c r="G127" s="16">
+        <f>G103</f>
+        <v/>
+      </c>
+      <c r="H127" s="16">
+        <f>H103</f>
+        <v/>
+      </c>
+      <c r="I127" s="16">
+        <f>I103</f>
+        <v/>
+      </c>
+      <c r="J127" s="16">
+        <f>J103</f>
+        <v/>
+      </c>
+      <c r="K127" s="16">
+        <f>K103</f>
+        <v/>
+      </c>
+      <c r="L127" s="16">
+        <f>L103</f>
+        <v/>
+      </c>
+      <c r="M127" s="16">
+        <f>M103</f>
+        <v/>
+      </c>
+      <c r="N127" s="16">
+        <f>N103+D124</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Equity Cash Flow</t>
+          <t>Levered IRR</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="16" t="inlineStr"/>
-      <c r="E128" s="16" t="inlineStr"/>
-      <c r="F128" s="16" t="inlineStr"/>
-      <c r="G128" s="16" t="inlineStr"/>
-      <c r="H128" s="16" t="inlineStr"/>
-      <c r="I128" s="16" t="inlineStr"/>
-      <c r="J128" s="16" t="inlineStr"/>
-      <c r="K128" s="16" t="inlineStr"/>
-      <c r="L128" s="16" t="inlineStr"/>
-      <c r="M128" s="16" t="inlineStr"/>
-      <c r="N128" s="16" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D128" s="28" t="n"/>
+      <c r="E128" s="16" t="n"/>
+      <c r="F128" s="16" t="n"/>
+      <c r="G128" s="16" t="n"/>
+      <c r="H128" s="16" t="n"/>
+      <c r="I128" s="16" t="n"/>
+      <c r="J128" s="16" t="n"/>
+      <c r="K128" s="16" t="n"/>
+      <c r="L128" s="16" t="n"/>
+      <c r="M128" s="16" t="n"/>
+      <c r="N128" s="16" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr"/>
-      <c r="D129" s="28" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Sum inflows / outflow</t>
+        </is>
+      </c>
+      <c r="D129" s="27" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>Sum inflows / outflow</t>
-        </is>
-      </c>
-      <c r="D130" s="27" t="inlineStr"/>
-    </row>
-    <row r="131"/>
+      <c r="A130" s="5" t="n"/>
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="27" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>Unlevered Returns (for reference)</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
+    </row>
     <row r="132">
-      <c r="A132" s="20" t="inlineStr">
-        <is>
-          <t>Unlevered Returns (for reference)</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr"/>
-      <c r="C132" s="6" t="inlineStr"/>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="16">
+        <f>-$D$27-D108</f>
+        <v/>
+      </c>
+      <c r="E132" s="16">
+        <f>E83</f>
+        <v/>
+      </c>
+      <c r="F132" s="16">
+        <f>F83</f>
+        <v/>
+      </c>
+      <c r="G132" s="16">
+        <f>G83</f>
+        <v/>
+      </c>
+      <c r="H132" s="16">
+        <f>H83</f>
+        <v/>
+      </c>
+      <c r="I132" s="16">
+        <f>I83</f>
+        <v/>
+      </c>
+      <c r="J132" s="16">
+        <f>J83</f>
+        <v/>
+      </c>
+      <c r="K132" s="16">
+        <f>K83</f>
+        <v/>
+      </c>
+      <c r="L132" s="16">
+        <f>L83</f>
+        <v/>
+      </c>
+      <c r="M132" s="16">
+        <f>M83</f>
+        <v/>
+      </c>
+      <c r="N132" s="16">
+        <f>N83+D121</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr"/>
-      <c r="D133" s="16">
-        <f>-$D$17-D98</f>
-        <v/>
-      </c>
-      <c r="E133" s="16">
-        <f>E73</f>
-        <v/>
-      </c>
-      <c r="F133" s="16">
-        <f>F73</f>
-        <v/>
-      </c>
-      <c r="G133" s="16">
-        <f>G73</f>
-        <v/>
-      </c>
-      <c r="H133" s="16">
-        <f>H73</f>
-        <v/>
-      </c>
-      <c r="I133" s="16">
-        <f>I73</f>
-        <v/>
-      </c>
-      <c r="J133" s="16">
-        <f>J73</f>
-        <v/>
-      </c>
-      <c r="K133" s="16">
-        <f>K73</f>
-        <v/>
-      </c>
-      <c r="L133" s="16">
-        <f>L73</f>
-        <v/>
-      </c>
-      <c r="M133" s="16">
-        <f>M73</f>
-        <v/>
-      </c>
-      <c r="N133" s="16">
-        <f>N73+N111</f>
-        <v/>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D133" s="28">
+        <f>IRR(D132:N132)</f>
+        <v/>
+      </c>
+      <c r="E133" s="16" t="n"/>
+      <c r="F133" s="16" t="n"/>
+      <c r="G133" s="16" t="n"/>
+      <c r="H133" s="16" t="n"/>
+      <c r="I133" s="16" t="n"/>
+      <c r="J133" s="16" t="n"/>
+      <c r="K133" s="16" t="n"/>
+      <c r="L133" s="16" t="n"/>
+      <c r="M133" s="16" t="n"/>
+      <c r="N133" s="16" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr"/>
-      <c r="D134" s="28" t="inlineStr"/>
-    </row>
+      <c r="A134" s="5" t="n"/>
+      <c r="B134" s="6" t="n"/>
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="28" t="n"/>
+    </row>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -3053,7 +3053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3456,7 +3456,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="10">
-        <f>IF(N81&lt;1,"PASS","FAIL")</f>
+        <f>IF(N91&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -3483,7 +3483,6 @@
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -6116,32 +6115,6 @@
       <c r="C134" s="6" t="n"/>
       <c r="D134" s="28" t="n"/>
     </row>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -3432,10 +3432,7 @@
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="10">
-        <f>D108</f>
-        <v/>
-      </c>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
@@ -3473,7 +3470,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.30,"PASS","FAIL")</f>
+        <f>IF(MINIFS(E92:N92,E92:N92,"&gt;0")&gt;=1.3,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_3_SolarBESS.xlsx
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -236,6 +236,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3231,10 +3232,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="n"/>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="55">
+        <f>IF(COUNTIF(E92:N92,"&gt;0")&gt;0,MINIFS(E92:N92,E92:N92,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="47" t="inlineStr">
@@ -3470,7 +3486,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(MINIFS(E92:N92,E92:N92,"&gt;0")&gt;=1.3,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.3,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
